--- a/school enrolment.xlsx
+++ b/school enrolment.xlsx
@@ -3361,7 +3361,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>रा.उ.मा.वि. छाछून्दरा (GOVT. SENIOR SECONDARY SCHOOL CHHACHHUNDRA)</t>
+          <t>रा.उ.मा.वि. छछून्दरा (GOVT. SENIOR SECONDARY SCHOOL CHHACHHUNDRA)</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>रा.उ.मा.वि. घाणा (GOVT. SENIOR SECONDARY SCHOOL GHANA)</t>
+          <t>रा.उ.मा.वि. घणा (GOVT. SENIOR SECONDARY SCHOOL GHANA)</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">

--- a/school enrolment.xlsx
+++ b/school enrolment.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,8 +77,60 @@
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F497D"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001B365D"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00274E13"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -145,8 +197,56 @@
         <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F497D"/>
+        <bgColor rgb="001F497D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE6F1"/>
+        <bgColor rgb="00DCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2DCDB"/>
+        <bgColor rgb="00F2DCDB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004A235A"/>
+        <bgColor rgb="004A235A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8DAEF"/>
+        <bgColor rgb="00E8DAEF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="19">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -364,11 +464,53 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="001F497D"/>
+      </left>
+      <right style="medium">
+        <color rgb="001F497D"/>
+      </right>
+      <top style="medium">
+        <color rgb="001F497D"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001F497D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -507,6 +649,103 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2435,7 +2674,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:Q71"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="26" min="1" max="1"/>
     <col width="15" customWidth="1" style="26" min="2" max="2"/>
@@ -2443,106 +2682,107 @@
     <col width="22" customWidth="1" style="26" min="4" max="4"/>
     <col width="26" customWidth="1" style="26" min="5" max="5"/>
     <col width="18" customWidth="1" style="26" min="6" max="6"/>
-    <col width="37.08984375" bestFit="1" customWidth="1" style="26" min="7" max="7"/>
+    <col width="30" customWidth="1" style="26" min="7" max="7"/>
     <col width="13" customWidth="1" style="26" min="8" max="8"/>
     <col width="14" customWidth="1" style="26" min="9" max="9"/>
     <col width="11" customWidth="1" style="26" min="10" max="10"/>
     <col width="14" customWidth="1" style="26" min="12" max="12"/>
     <col width="11" customWidth="1" style="26" min="13" max="13"/>
-    <col width="15" customWidth="1" style="26" min="14" max="15"/>
+    <col width="15" customWidth="1" style="26" min="14" max="14"/>
+    <col width="15" customWidth="1" style="26" min="15" max="15"/>
     <col width="12" customWidth="1" style="26" min="16" max="16"/>
     <col width="36" customWidth="1" style="26" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" s="26">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="56" t="inlineStr">
         <is>
           <t>कार्यालय मुख्य ब्लॉक शिक्षा अधिकारी (CBEO), भिनाय (अजमेर)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" s="26">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="57" t="inlineStr">
         <is>
           <t>समान परीक्षा (2026-27) मांग बनाम शाला दर्पण नामांकन मिलान एवं अंतर विश्लेषण रिपोर्ट (मय संस्था प्रधान संपर्क विवरण)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" s="26">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>जिला: अजमेर (AJMER) | ब्लॉक: भिनाय (BHINAI) | कुल राजकीय विद्यालय: 49 | कुल निजी विद्यालय: 8</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" s="26">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="59" t="inlineStr">
         <is>
           <t>भाग - 1 : राजकीय माध्यमिक एवं उच्च माध्यमिक विद्यालय (49 विद्यालय) - नामांकन बनाम परीक्षा मांग मिलान एवं संस्था प्रधान विवरण</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" s="26">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>क्र.सं.</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>शाला दर्पण कोड</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="60" t="inlineStr">
         <is>
           <t>विद्यालय का सही नाम (School Official Hindi &amp; English Name)</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="60" t="inlineStr">
         <is>
           <t>PEEO परिक्षेत्र</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="61" t="inlineStr">
         <is>
           <t>संस्था प्रधान का नाम
 (Principal / HM)</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="61" t="inlineStr">
         <is>
           <t>संस्था प्रधान मोबाइल
 (Principal Mobile)</t>
         </is>
       </c>
-      <c r="G5" s="23" t="inlineStr">
+      <c r="G5" s="61" t="inlineStr">
         <is>
           <t>परीक्षा प्रभारी मोबाइल
 (Exam Incharge Mobile)</t>
         </is>
       </c>
-      <c r="H5" s="32" t="inlineStr">
+      <c r="H5" s="62" t="inlineStr">
         <is>
           <t>कक्षा 9 एवं 10 मिलान</t>
         </is>
       </c>
-      <c r="I5" s="49" t="n"/>
-      <c r="J5" s="50" t="n"/>
-      <c r="K5" s="38" t="inlineStr">
+      <c r="I5" s="63" t="n"/>
+      <c r="J5" s="63" t="n"/>
+      <c r="K5" s="64" t="inlineStr">
         <is>
           <t>कक्षा 11 एवं 12 मिलान</t>
         </is>
       </c>
-      <c r="L5" s="49" t="n"/>
-      <c r="M5" s="50" t="n"/>
-      <c r="N5" s="29" t="inlineStr">
+      <c r="L5" s="63" t="n"/>
+      <c r="M5" s="63" t="n"/>
+      <c r="N5" s="65" t="inlineStr">
         <is>
           <t>कुल विद्यार्थी संख्या (कक्षा 9 से 12)</t>
         </is>
       </c>
-      <c r="O5" s="49" t="n"/>
-      <c r="P5" s="50" t="n"/>
-      <c r="Q5" s="27" t="inlineStr">
+      <c r="O5" s="63" t="n"/>
+      <c r="P5" s="63" t="n"/>
+      <c r="Q5" s="60" t="inlineStr">
         <is>
           <t>अंतर स्थिति व टिप्पणी
 (Remarks / Status)</t>
@@ -2550,4229 +2790,4227 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" s="26">
-      <c r="A6" s="51" t="n"/>
-      <c r="B6" s="51" t="n"/>
-      <c r="C6" s="51" t="n"/>
-      <c r="D6" s="51" t="n"/>
-      <c r="E6" s="51" t="n"/>
-      <c r="F6" s="51" t="n"/>
-      <c r="G6" s="51" t="n"/>
-      <c r="H6" s="32" t="inlineStr">
+      <c r="A6" s="63" t="n"/>
+      <c r="B6" s="63" t="n"/>
+      <c r="C6" s="63" t="n"/>
+      <c r="D6" s="63" t="n"/>
+      <c r="E6" s="63" t="n"/>
+      <c r="F6" s="63" t="n"/>
+      <c r="G6" s="63" t="n"/>
+      <c r="H6" s="62" t="inlineStr">
         <is>
           <t>नामांकन
 (9-10)</t>
         </is>
       </c>
-      <c r="I6" s="32" t="inlineStr">
+      <c r="I6" s="62" t="inlineStr">
         <is>
           <t>समान परीक्षा
 (9+10)</t>
         </is>
       </c>
-      <c r="J6" s="32" t="inlineStr">
+      <c r="J6" s="62" t="inlineStr">
         <is>
           <t>अंतर
 (Diff)</t>
         </is>
       </c>
-      <c r="K6" s="38" t="inlineStr">
+      <c r="K6" s="64" t="inlineStr">
         <is>
           <t>नामांकन
 (11-12)</t>
         </is>
       </c>
-      <c r="L6" s="38" t="inlineStr">
+      <c r="L6" s="64" t="inlineStr">
         <is>
           <t>समान परीक्षा
 (11+12)</t>
         </is>
       </c>
-      <c r="M6" s="38" t="inlineStr">
+      <c r="M6" s="64" t="inlineStr">
         <is>
           <t>अंतर
 (Diff)</t>
         </is>
       </c>
-      <c r="N6" s="29" t="inlineStr">
+      <c r="N6" s="65" t="inlineStr">
         <is>
           <t>कुल नामांकन
 (9-12)</t>
         </is>
       </c>
-      <c r="O6" s="29" t="inlineStr">
+      <c r="O6" s="65" t="inlineStr">
         <is>
           <t>समान परीक्षा
 कुल मांग</t>
         </is>
       </c>
-      <c r="P6" s="29" t="inlineStr">
+      <c r="P6" s="65" t="inlineStr">
         <is>
           <t>कुल अंतर
 (Net Diff)</t>
         </is>
       </c>
-      <c r="Q6" s="51" t="n"/>
+      <c r="Q6" s="63" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="66" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="66" t="inlineStr">
         <is>
           <t>506830</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="67" t="inlineStr">
         <is>
           <t>रा.बा.उ.मा.वि. बड़ली (GOVT. GIRLS SENIOR SECONDARY SCHOOL BADLI)</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="67" t="inlineStr">
         <is>
           <t>PEEO BARLI</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="67" t="inlineStr">
         <is>
           <t>PUKHRAJ KHATI</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="66" t="inlineStr">
         <is>
           <t>9667157047</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="67" t="inlineStr">
         <is>
           <t>RAJENDRA NATH SIDH (9783601902)</t>
         </is>
       </c>
-      <c r="H7" s="7" t="n">
+      <c r="H7" s="68" t="n">
         <v>86</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="68" t="n">
         <v>86</v>
       </c>
-      <c r="J7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="7" t="n">
+      <c r="J7" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="68" t="n">
         <v>43</v>
       </c>
-      <c r="L7" s="7" t="n">
+      <c r="L7" s="68" t="n">
         <v>43</v>
       </c>
-      <c r="M7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="7" t="n">
+      <c r="M7" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="68" t="n">
         <v>129</v>
       </c>
-      <c r="O7" s="7" t="n">
+      <c r="O7" s="68" t="n">
         <v>129</v>
       </c>
-      <c r="P7" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="P7" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="66" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="66" t="inlineStr">
         <is>
           <t>494626</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="67" t="inlineStr">
         <is>
           <t>रा.बा.उ.मा.वि. चापानेरी (GOVT. GIRLS SENIOR SECONDARY SCHOOL CHAPANERI)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="67" t="inlineStr">
         <is>
           <t>PEEO CHAPANERI</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="67" t="inlineStr">
         <is>
           <t>HARI SHANKAR CHOPDAR</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="66" t="inlineStr">
         <is>
           <t>9602676785</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="67" t="inlineStr">
         <is>
           <t>Ramji lal (9460381436)</t>
         </is>
       </c>
-      <c r="H8" s="7" t="n">
+      <c r="H8" s="68" t="n">
         <v>59</v>
       </c>
-      <c r="I8" s="7" t="n">
+      <c r="I8" s="68" t="n">
         <v>59</v>
       </c>
-      <c r="J8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="7" t="n">
+      <c r="J8" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="68" t="n">
         <v>28</v>
       </c>
-      <c r="L8" s="7" t="n">
+      <c r="L8" s="68" t="n">
         <v>28</v>
       </c>
-      <c r="M8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="7" t="n">
+      <c r="M8" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="68" t="n">
         <v>87</v>
       </c>
-      <c r="O8" s="7" t="n">
+      <c r="O8" s="68" t="n">
         <v>87</v>
       </c>
-      <c r="P8" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="9" t="inlineStr">
+      <c r="P8" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="66" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="66" t="inlineStr">
         <is>
           <t>488791</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="67" t="inlineStr">
         <is>
           <t>रा.बा.उ.मा.वि. खेड़ी (GOVT. GIRLS SENIOR SECONDARY SCHOOL KHEDI)</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="67" t="inlineStr">
         <is>
           <t>PEEO KARATI</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="67" t="inlineStr">
         <is>
           <t>श्री हंस राज गुर्जर (प्रभारी संस्था प्रधान)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="66" t="inlineStr">
         <is>
           <t>8890478933</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="67" t="inlineStr">
         <is>
           <t>श्रीमती चंचल कच्छावा (8003070002)</t>
         </is>
       </c>
-      <c r="H9" s="7" t="n">
+      <c r="H9" s="68" t="n">
         <v>41</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="68" t="n">
         <v>41</v>
       </c>
-      <c r="J9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="7" t="n">
+      <c r="J9" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="68" t="n">
         <v>17</v>
       </c>
-      <c r="L9" s="7" t="n">
+      <c r="L9" s="68" t="n">
         <v>17</v>
       </c>
-      <c r="M9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="7" t="n">
+      <c r="M9" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="68" t="n">
         <v>58</v>
       </c>
-      <c r="O9" s="7" t="n">
+      <c r="O9" s="68" t="n">
         <v>58</v>
       </c>
-      <c r="P9" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="9" t="inlineStr">
+      <c r="P9" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="66" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="66" t="inlineStr">
         <is>
           <t>410632</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="67" t="inlineStr">
         <is>
           <t>रा.बा.उ.मा.वि. नांदसी (GOVT. GIRLS SENIOR SECONDARY SCHOOL NANDSI)</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="67" t="inlineStr">
         <is>
           <t>PEEO NANDSI</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="67" t="inlineStr">
         <is>
           <t>JITENDRA KUMAR SHARMA</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="66" t="inlineStr">
         <is>
           <t>7073800244</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="67" t="inlineStr">
         <is>
           <t>BALKARAN SINGH (8875634183)</t>
         </is>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H10" s="68" t="n">
         <v>43</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="68" t="n">
         <v>43</v>
       </c>
-      <c r="J10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="7" t="n">
+      <c r="J10" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="68" t="n">
         <v>26</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="L10" s="68" t="n">
         <v>26</v>
       </c>
-      <c r="M10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="7" t="n">
+      <c r="M10" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="68" t="n">
         <v>69</v>
       </c>
-      <c r="O10" s="7" t="n">
+      <c r="O10" s="68" t="n">
         <v>69</v>
       </c>
-      <c r="P10" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="9" t="inlineStr">
+      <c r="P10" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="66" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="66" t="inlineStr">
         <is>
           <t>221764</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. बड़गांव (सूरखण्ड) (GOVT. SENIOR SECONDARY SCHOOL BADGAON - SURKHAND)</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="67" t="inlineStr">
         <is>
           <t>PEEO BARGAON</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="67" t="inlineStr">
         <is>
           <t>CHANDRA PRAKASH LADDHA</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="66" t="inlineStr">
         <is>
           <t>9001450275</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="67" t="inlineStr">
         <is>
           <t>DR. VIJAY SHANKAR SHARMA (9928191102)</t>
         </is>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="68" t="n">
         <v>165</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="68" t="n">
         <v>165</v>
       </c>
-      <c r="J11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="7" t="n">
+      <c r="J11" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="68" t="n">
         <v>96</v>
       </c>
-      <c r="L11" s="7" t="n">
+      <c r="L11" s="68" t="n">
         <v>96</v>
       </c>
-      <c r="M11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="7" t="n">
+      <c r="M11" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="68" t="n">
         <v>261</v>
       </c>
-      <c r="O11" s="7" t="n">
+      <c r="O11" s="68" t="n">
         <v>261</v>
       </c>
-      <c r="P11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="9" t="inlineStr">
+      <c r="P11" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="66" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="66" t="inlineStr">
         <is>
           <t>488781</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. बडला (नागोला) (GOVT. SENIOR SECONDARY SCHOOL BADLA)</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="67" t="inlineStr">
         <is>
           <t>PEEO NAGOLA</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="67" t="inlineStr">
         <is>
           <t>VED PRAKASH</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="66" t="inlineStr">
         <is>
           <t>9413682497</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="67" t="inlineStr">
         <is>
           <t>Hanuman ram (9660242634)</t>
         </is>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H12" s="68" t="n">
         <v>60</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="68" t="n">
         <v>60</v>
       </c>
-      <c r="J12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="7" t="n">
+      <c r="J12" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="68" t="n">
         <v>28</v>
       </c>
-      <c r="L12" s="7" t="n">
+      <c r="L12" s="68" t="n">
         <v>28</v>
       </c>
-      <c r="M12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="7" t="n">
+      <c r="M12" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="68" t="n">
         <v>88</v>
       </c>
-      <c r="O12" s="7" t="n">
+      <c r="O12" s="68" t="n">
         <v>88</v>
       </c>
-      <c r="P12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="9" t="inlineStr">
+      <c r="P12" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="66" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="66" t="inlineStr">
         <is>
           <t>221755</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. बड़ली (GOVT. SENIOR SECONDARY SCHOOL BADLI)</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="67" t="inlineStr">
         <is>
           <t>PEEO BARLI</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="67" t="inlineStr">
         <is>
           <t>SHAILENDRA KUMAR PANDYA</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="66" t="inlineStr">
         <is>
           <t>9950985201</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="67" t="inlineStr">
         <is>
           <t>KUSUM PAREEK (9414312452)</t>
         </is>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H13" s="68" t="n">
         <v>85</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I13" s="68" t="n">
         <v>85</v>
       </c>
-      <c r="J13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="7" t="n">
+      <c r="J13" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="68" t="n">
         <v>52</v>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="L13" s="68" t="n">
         <v>52</v>
       </c>
-      <c r="M13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="7" t="n">
+      <c r="M13" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="68" t="n">
         <v>137</v>
       </c>
-      <c r="O13" s="7" t="n">
+      <c r="O13" s="68" t="n">
         <v>137</v>
       </c>
-      <c r="P13" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="9" t="inlineStr">
+      <c r="P13" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="66" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="66" t="inlineStr">
         <is>
           <t>221769</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. बांदनवाड़ा (GOVT. SENIOR SECONDARY SCHOOL BANDANWARA)</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="67" t="inlineStr">
         <is>
           <t>PEEO BANDANWARA</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="67" t="inlineStr">
         <is>
           <t>BHANWAR LAL JAT</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="66" t="inlineStr">
         <is>
           <t>9587293842</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="67" t="inlineStr">
         <is>
           <t>VINITA NAMA (7891806611)</t>
         </is>
       </c>
-      <c r="H14" s="7" t="n">
+      <c r="H14" s="68" t="n">
         <v>187</v>
       </c>
-      <c r="I14" s="7" t="n">
+      <c r="I14" s="68" t="n">
         <v>187</v>
       </c>
-      <c r="J14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="7" t="n">
+      <c r="J14" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="68" t="n">
         <v>132</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="L14" s="68" t="n">
         <v>132</v>
       </c>
-      <c r="M14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="7" t="n">
+      <c r="M14" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="68" t="n">
         <v>319</v>
       </c>
-      <c r="O14" s="7" t="n">
+      <c r="O14" s="68" t="n">
         <v>319</v>
       </c>
-      <c r="P14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
+      <c r="P14" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
-    <row r="15" customFormat="1" s="47">
-      <c r="A15" s="42" t="n">
+    <row r="15">
+      <c r="A15" s="66" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="42" t="inlineStr">
+      <c r="B15" s="66" t="inlineStr">
         <is>
           <t>221780</t>
         </is>
       </c>
-      <c r="C15" s="43" t="inlineStr">
+      <c r="C15" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. भिनाय (GOVT. SENIOR SECONDARY SCHOOL BHINAI)</t>
         </is>
       </c>
-      <c r="D15" s="43" t="inlineStr">
+      <c r="D15" s="67" t="inlineStr">
         <is>
           <t>PEEO BHINAY</t>
         </is>
       </c>
-      <c r="E15" s="43" t="inlineStr">
+      <c r="E15" s="67" t="inlineStr">
         <is>
           <t>AJAY KUMAR DHABAI</t>
         </is>
       </c>
-      <c r="F15" s="42" t="inlineStr">
+      <c r="F15" s="66" t="inlineStr">
         <is>
           <t>9549240545</t>
         </is>
       </c>
-      <c r="G15" s="43" t="inlineStr">
+      <c r="G15" s="67" t="inlineStr">
         <is>
           <t>Chandrawati Tejwani (9413694262)</t>
         </is>
       </c>
-      <c r="H15" s="44" t="n">
+      <c r="H15" s="68" t="n">
         <v>223</v>
       </c>
-      <c r="I15" s="44" t="n">
+      <c r="I15" s="68" t="n">
         <v>232</v>
       </c>
-      <c r="J15" s="45" t="n">
+      <c r="J15" s="71" t="n">
         <v>9</v>
       </c>
-      <c r="K15" s="44" t="n">
+      <c r="K15" s="68" t="n">
         <v>178</v>
       </c>
-      <c r="L15" s="44" t="n">
+      <c r="L15" s="68" t="n">
         <v>179</v>
       </c>
-      <c r="M15" s="45" t="n">
+      <c r="M15" s="71" t="n">
         <v>1</v>
       </c>
-      <c r="N15" s="44" t="n">
+      <c r="N15" s="68" t="n">
         <v>401</v>
       </c>
-      <c r="O15" s="44" t="n">
+      <c r="O15" s="68" t="n">
         <v>411</v>
       </c>
-      <c r="P15" s="45" t="n">
+      <c r="P15" s="71" t="n">
         <v>10</v>
       </c>
-      <c r="Q15" s="46" t="inlineStr">
+      <c r="Q15" s="72" t="inlineStr">
         <is>
           <t>अंतर: +10 (9-10 में +9, 11-12 में +1)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="66" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="66" t="inlineStr">
         <is>
           <t>221763</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. बूबकिया (GOVT. SENIOR SECONDARY SCHOOL BOOBKIYA)</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="67" t="inlineStr">
         <is>
           <t>PEEO BOOBKIYA</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="67" t="inlineStr">
         <is>
           <t>RAM CHANDRA GUJAR</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="66" t="inlineStr">
         <is>
           <t>9252068645</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="67" t="inlineStr">
         <is>
           <t>Dinesh kumar kumawat (9829896189)</t>
         </is>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="H16" s="68" t="n">
         <v>104</v>
       </c>
-      <c r="I16" s="7" t="n">
+      <c r="I16" s="68" t="n">
         <v>104</v>
       </c>
-      <c r="J16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="7" t="n">
+      <c r="J16" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="68" t="n">
         <v>44</v>
       </c>
-      <c r="L16" s="7" t="n">
+      <c r="L16" s="68" t="n">
         <v>44</v>
       </c>
-      <c r="M16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="7" t="n">
+      <c r="M16" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="68" t="n">
         <v>148</v>
       </c>
-      <c r="O16" s="7" t="n">
+      <c r="O16" s="68" t="n">
         <v>148</v>
       </c>
-      <c r="P16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="9" t="inlineStr">
+      <c r="P16" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
-    <row r="17" customFormat="1" s="47">
-      <c r="A17" s="42" t="n">
+    <row r="17">
+      <c r="A17" s="66" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="42" t="inlineStr">
+      <c r="B17" s="66" t="inlineStr">
         <is>
           <t>221758</t>
         </is>
       </c>
-      <c r="C17" s="43" t="inlineStr">
+      <c r="C17" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. चापानेरी (GOVT. SENIOR SECONDARY SCHOOL CHAPANERI)</t>
         </is>
       </c>
-      <c r="D17" s="43" t="inlineStr">
+      <c r="D17" s="67" t="inlineStr">
         <is>
           <t>PEEO CHAPANERI</t>
         </is>
       </c>
-      <c r="E17" s="43" t="inlineStr">
+      <c r="E17" s="67" t="inlineStr">
         <is>
           <t>LADURAM SHARMA</t>
         </is>
       </c>
-      <c r="F17" s="42" t="inlineStr">
+      <c r="F17" s="66" t="inlineStr">
         <is>
           <t>9462507510</t>
         </is>
       </c>
-      <c r="G17" s="43" t="inlineStr">
+      <c r="G17" s="67" t="inlineStr">
         <is>
           <t>GOVIND RAM JANGID (9982323026)</t>
         </is>
       </c>
-      <c r="H17" s="44" t="n">
+      <c r="H17" s="68" t="n">
         <v>115</v>
       </c>
-      <c r="I17" s="44" t="n">
+      <c r="I17" s="68" t="n">
         <v>116</v>
       </c>
-      <c r="J17" s="45" t="n">
+      <c r="J17" s="71" t="n">
         <v>1</v>
       </c>
-      <c r="K17" s="44" t="n">
+      <c r="K17" s="68" t="n">
         <v>59</v>
       </c>
-      <c r="L17" s="44" t="n">
+      <c r="L17" s="68" t="n">
         <v>59</v>
       </c>
-      <c r="M17" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="44" t="n">
+      <c r="M17" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="68" t="n">
         <v>174</v>
       </c>
-      <c r="O17" s="44" t="n">
+      <c r="O17" s="68" t="n">
         <v>175</v>
       </c>
-      <c r="P17" s="45" t="n">
+      <c r="P17" s="71" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" s="46" t="inlineStr">
+      <c r="Q17" s="72" t="inlineStr">
         <is>
           <t>अंतर: +1 (9-10 में +1)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="66" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="66" t="inlineStr">
         <is>
           <t>221787</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. छछून्दरा (GOVT. SENIOR SECONDARY SCHOOL CHHACHHUNDRA)</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="67" t="inlineStr">
         <is>
           <t>PEEO CHHACHHUNDRA</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="67" t="inlineStr">
         <is>
           <t>SITARAM DHOBI</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="66" t="inlineStr">
         <is>
           <t>9413781124</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="67" t="inlineStr">
         <is>
           <t>LALITA MAHAWAR (9785313155)</t>
         </is>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="H18" s="68" t="n">
         <v>106</v>
       </c>
-      <c r="I18" s="7" t="n">
+      <c r="I18" s="68" t="n">
         <v>106</v>
       </c>
-      <c r="J18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="7" t="n">
+      <c r="J18" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="68" t="n">
         <v>62</v>
       </c>
-      <c r="L18" s="7" t="n">
+      <c r="L18" s="68" t="n">
         <v>62</v>
       </c>
-      <c r="M18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="7" t="n">
+      <c r="M18" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="68" t="n">
         <v>168</v>
       </c>
-      <c r="O18" s="7" t="n">
+      <c r="O18" s="68" t="n">
         <v>168</v>
       </c>
-      <c r="P18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="9" t="inlineStr">
+      <c r="P18" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="66" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="66" t="inlineStr">
         <is>
           <t>488941</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. देवरिया (GOVT. SENIOR SECONDARY SCHOOL DEVRIYA)</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="67" t="inlineStr">
         <is>
           <t>PEEO DEVPURA</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="67" t="inlineStr">
         <is>
           <t>ANITA SHARMA</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="66" t="inlineStr">
         <is>
           <t>9414550658</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="67" t="inlineStr">
         <is>
           <t>Ankita Verma (9468695037)</t>
         </is>
       </c>
-      <c r="H19" s="7" t="n">
+      <c r="H19" s="68" t="n">
         <v>56</v>
       </c>
-      <c r="I19" s="7" t="n">
+      <c r="I19" s="68" t="n">
         <v>56</v>
       </c>
-      <c r="J19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="7" t="n">
+      <c r="J19" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="68" t="n">
         <v>23</v>
       </c>
-      <c r="L19" s="7" t="n">
+      <c r="L19" s="68" t="n">
         <v>23</v>
       </c>
-      <c r="M19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="7" t="n">
+      <c r="M19" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="68" t="n">
         <v>79</v>
       </c>
-      <c r="O19" s="7" t="n">
+      <c r="O19" s="68" t="n">
         <v>79</v>
       </c>
-      <c r="P19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="9" t="inlineStr">
+      <c r="P19" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="66" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="66" t="inlineStr">
         <is>
           <t>221783</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. धांतोल (GOVT. SENIOR SECONDARY SCHOOL DHANTOL)</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="67" t="inlineStr">
         <is>
           <t>PEEO DHANTOL</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="67" t="inlineStr">
         <is>
           <t>SURENDRA NAGORA</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="66" t="inlineStr">
         <is>
           <t>9413695182</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="67" t="inlineStr">
         <is>
           <t>Poonam (8107141066)</t>
         </is>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="H20" s="68" t="n">
         <v>84</v>
       </c>
-      <c r="I20" s="7" t="n">
+      <c r="I20" s="68" t="n">
         <v>84</v>
       </c>
-      <c r="J20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="7" t="n">
+      <c r="J20" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="68" t="n">
         <v>39</v>
       </c>
-      <c r="L20" s="7" t="n">
+      <c r="L20" s="68" t="n">
         <v>39</v>
       </c>
-      <c r="M20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="7" t="n">
+      <c r="M20" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="68" t="n">
         <v>123</v>
       </c>
-      <c r="O20" s="7" t="n">
+      <c r="O20" s="68" t="n">
         <v>123</v>
       </c>
-      <c r="P20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="9" t="inlineStr">
+      <c r="P20" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="66" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="66" t="inlineStr">
         <is>
           <t>221786</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. एकलसिंघा (GOVT. SENIOR SECONDARY SCHOOL EKALSINGHA)</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="67" t="inlineStr">
         <is>
           <t>PEEO EKALSEENGA</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="67" t="inlineStr">
         <is>
           <t>VISHWASHWAR PRASAD SHARMA</t>
         </is>
       </c>
-      <c r="F21" s="5" t="inlineStr">
+      <c r="F21" s="66" t="inlineStr">
         <is>
           <t>7728052397</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="67" t="inlineStr">
         <is>
           <t>MANJU CHOUDHARY (8107003655)</t>
         </is>
       </c>
-      <c r="H21" s="7" t="n">
+      <c r="H21" s="68" t="n">
         <v>145</v>
       </c>
-      <c r="I21" s="7" t="n">
+      <c r="I21" s="68" t="n">
         <v>145</v>
       </c>
-      <c r="J21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="7" t="n">
+      <c r="J21" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="68" t="n">
         <v>69</v>
       </c>
-      <c r="L21" s="7" t="n">
+      <c r="L21" s="68" t="n">
         <v>69</v>
       </c>
-      <c r="M21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="7" t="n">
+      <c r="M21" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="68" t="n">
         <v>214</v>
       </c>
-      <c r="O21" s="7" t="n">
+      <c r="O21" s="68" t="n">
         <v>214</v>
       </c>
-      <c r="P21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="9" t="inlineStr">
+      <c r="P21" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="66" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="66" t="inlineStr">
         <is>
           <t>221760</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. गनाहेड़ा (GOVT. SENIOR SECONDARY SCHOOL GANAHERA)</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="67" t="inlineStr">
         <is>
           <t>PEEO LAMGARA</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="67" t="inlineStr">
         <is>
           <t>RASHMI MALVIYA</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="66" t="inlineStr">
         <is>
           <t>9461981723</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="67" t="inlineStr">
         <is>
           <t>Alka kumari choudhary (9460357416)</t>
         </is>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="H22" s="68" t="n">
         <v>50</v>
       </c>
-      <c r="I22" s="7" t="n">
+      <c r="I22" s="68" t="n">
         <v>50</v>
       </c>
-      <c r="J22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="7" t="n">
+      <c r="J22" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="68" t="n">
         <v>44</v>
       </c>
-      <c r="L22" s="7" t="n">
+      <c r="L22" s="68" t="n">
         <v>44</v>
       </c>
-      <c r="M22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="7" t="n">
+      <c r="M22" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="68" t="n">
         <v>94</v>
       </c>
-      <c r="O22" s="7" t="n">
+      <c r="O22" s="68" t="n">
         <v>94</v>
       </c>
-      <c r="P22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="9" t="inlineStr">
+      <c r="P22" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="66" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="66" t="inlineStr">
         <is>
           <t>488897</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. घणा (GOVT. SENIOR SECONDARY SCHOOL GHANA)</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="67" t="inlineStr">
         <is>
           <t>PEEO SOBRI</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="67" t="inlineStr">
         <is>
           <t>SUMITRA KUMARI PHULWARI</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F23" s="66" t="inlineStr">
         <is>
           <t>9928994663</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="67" t="inlineStr">
         <is>
           <t>Satyendra singh (9460660031)</t>
         </is>
       </c>
-      <c r="H23" s="7" t="n">
+      <c r="H23" s="68" t="n">
         <v>75</v>
       </c>
-      <c r="I23" s="7" t="n">
+      <c r="I23" s="68" t="n">
         <v>75</v>
       </c>
-      <c r="J23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="7" t="n">
+      <c r="J23" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="68" t="n">
         <v>53</v>
       </c>
-      <c r="L23" s="7" t="n">
+      <c r="L23" s="68" t="n">
         <v>53</v>
       </c>
-      <c r="M23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="7" t="n">
+      <c r="M23" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="68" t="n">
         <v>128</v>
       </c>
-      <c r="O23" s="7" t="n">
+      <c r="O23" s="68" t="n">
         <v>128</v>
       </c>
-      <c r="P23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="9" t="inlineStr">
+      <c r="P23" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="66" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="66" t="inlineStr">
         <is>
           <t>221762</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. गुढ़ा खुर्द (GOVT. SENIOR SECONDARY SCHOOL GUDHA KHURD)</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="67" t="inlineStr">
         <is>
           <t>PEEO GURHA KHURD</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="67" t="inlineStr">
         <is>
           <t>Deepesh Kumar Sisodia</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F24" s="66" t="inlineStr">
         <is>
           <t>9414554344</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="67" t="inlineStr">
         <is>
           <t>RAJANEESH KUMAR JANGID (9875119865)</t>
         </is>
       </c>
-      <c r="H24" s="7" t="n">
+      <c r="H24" s="68" t="n">
         <v>118</v>
       </c>
-      <c r="I24" s="7" t="n">
+      <c r="I24" s="68" t="n">
         <v>118</v>
       </c>
-      <c r="J24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="7" t="n">
+      <c r="J24" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="68" t="n">
         <v>104</v>
       </c>
-      <c r="L24" s="7" t="n">
+      <c r="L24" s="68" t="n">
         <v>104</v>
       </c>
-      <c r="M24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="7" t="n">
+      <c r="M24" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="68" t="n">
         <v>222</v>
       </c>
-      <c r="O24" s="7" t="n">
+      <c r="O24" s="68" t="n">
         <v>222</v>
       </c>
-      <c r="P24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="9" t="inlineStr">
+      <c r="P24" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="66" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="66" t="inlineStr">
         <is>
           <t>221784</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. हीरापुरा (GOVT. SENIOR SECONDARY SCHOOL HEERAPURA)</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="67" t="inlineStr">
         <is>
           <t>PEEO RAMMALIA</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="67" t="inlineStr">
         <is>
           <t>BHAGCHAND REGAR</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F25" s="66" t="inlineStr">
         <is>
           <t>9829219564</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="67" t="inlineStr">
         <is>
           <t>DHARMRAJ MEENA (9649201976)</t>
         </is>
       </c>
-      <c r="H25" s="7" t="n">
+      <c r="H25" s="68" t="n">
         <v>102</v>
       </c>
-      <c r="I25" s="7" t="n">
+      <c r="I25" s="68" t="n">
         <v>102</v>
       </c>
-      <c r="J25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="7" t="n">
+      <c r="J25" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="68" t="n">
         <v>31</v>
       </c>
-      <c r="L25" s="7" t="n">
+      <c r="L25" s="68" t="n">
         <v>31</v>
       </c>
-      <c r="M25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="7" t="n">
+      <c r="M25" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="68" t="n">
         <v>133</v>
       </c>
-      <c r="O25" s="7" t="n">
+      <c r="O25" s="68" t="n">
         <v>133</v>
       </c>
-      <c r="P25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="9" t="inlineStr">
+      <c r="P25" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="66" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="66" t="inlineStr">
         <is>
           <t>488947</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. हियालिया (GOVT. SENIOR SECONDARY SCHOOL HIYALIYA)</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="67" t="inlineStr">
         <is>
           <t>PEEO EKALSEENGA</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="67" t="inlineStr">
         <is>
           <t>SURESH CHANDRA</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="66" t="inlineStr">
         <is>
           <t>9636233704</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" s="67" t="inlineStr">
         <is>
           <t>RAJENDRA KUMAR SHARMA (9540386335)</t>
         </is>
       </c>
-      <c r="H26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="9" t="inlineStr">
+      <c r="H26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="66" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="66" t="inlineStr">
         <is>
           <t>221768</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. जेतपुरा (GOVT. SENIOR SECONDARY SCHOOL JETPURA)</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="67" t="inlineStr">
         <is>
           <t>PEEO KEROT</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="67" t="inlineStr">
         <is>
           <t>JUBER AHMED</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="66" t="inlineStr">
         <is>
           <t>9414942132</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" s="67" t="inlineStr">
         <is>
           <t>Gangaram regar (9929136369)</t>
         </is>
       </c>
-      <c r="H27" s="7" t="n">
+      <c r="H27" s="68" t="n">
         <v>44</v>
       </c>
-      <c r="I27" s="7" t="n">
+      <c r="I27" s="68" t="n">
         <v>44</v>
       </c>
-      <c r="J27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="7" t="n">
+      <c r="J27" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="68" t="n">
         <v>22</v>
       </c>
-      <c r="L27" s="7" t="n">
+      <c r="L27" s="68" t="n">
         <v>22</v>
       </c>
-      <c r="M27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="7" t="n">
+      <c r="M27" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="68" t="n">
         <v>66</v>
       </c>
-      <c r="O27" s="7" t="n">
+      <c r="O27" s="68" t="n">
         <v>66</v>
       </c>
-      <c r="P27" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="9" t="inlineStr">
+      <c r="P27" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="66" t="n">
         <v>22</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="66" t="inlineStr">
         <is>
           <t>221776</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. झीपिया (GOVT. SENIOR SECONDARY SCHOOL JHIPIYA)</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="67" t="inlineStr">
         <is>
           <t>PEEO RATAKOT</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="67" t="inlineStr">
         <is>
           <t>अलका माथुर (प्रभारी संस्था प्रधान)</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="66" t="inlineStr">
         <is>
           <t>9468751626</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G28" s="67" t="inlineStr">
         <is>
           <t>Himanshu Gurjar (7976582960)</t>
         </is>
       </c>
-      <c r="H28" s="7" t="n">
+      <c r="H28" s="68" t="n">
         <v>5</v>
       </c>
-      <c r="I28" s="7" t="n">
+      <c r="I28" s="68" t="n">
         <v>5</v>
       </c>
-      <c r="J28" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="7" t="n">
+      <c r="J28" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="68" t="n">
         <v>5</v>
       </c>
-      <c r="O28" s="7" t="n">
+      <c r="O28" s="68" t="n">
         <v>5</v>
       </c>
-      <c r="P28" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="9" t="inlineStr">
+      <c r="P28" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="66" t="n">
         <v>23</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="66" t="inlineStr">
         <is>
           <t>221767</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. कैरोट (जेतपुरा) (GOVT. SENIOR SECONDARY SCHOOL KAIROT GURJAR MOHALLA JATPURA ROAD)</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="67" t="inlineStr">
         <is>
           <t>PEEO KEROT</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" s="67" t="inlineStr">
         <is>
           <t>SOHANLAL SARAN</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="66" t="inlineStr">
         <is>
           <t>9929526324</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G29" s="67" t="inlineStr">
         <is>
           <t>Pankaj Tiwari (9928649547)</t>
         </is>
       </c>
-      <c r="H29" s="7" t="n">
+      <c r="H29" s="68" t="n">
         <v>64</v>
       </c>
-      <c r="I29" s="7" t="n">
+      <c r="I29" s="68" t="n">
         <v>64</v>
       </c>
-      <c r="J29" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="7" t="n">
+      <c r="J29" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="68" t="n">
         <v>34</v>
       </c>
-      <c r="L29" s="7" t="n">
+      <c r="L29" s="68" t="n">
         <v>34</v>
       </c>
-      <c r="M29" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="7" t="n">
+      <c r="M29" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="68" t="n">
         <v>98</v>
       </c>
-      <c r="O29" s="7" t="n">
+      <c r="O29" s="68" t="n">
         <v>98</v>
       </c>
-      <c r="P29" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="9" t="inlineStr">
+      <c r="P29" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="66" t="n">
         <v>24</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="66" t="inlineStr">
         <is>
           <t>221765</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. कनाई कलां (GOVT. SENIOR SECONDARY SCHOOL KANAI KALA)</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="67" t="inlineStr">
         <is>
           <t>PEEO KANAI KALAN</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="E30" s="67" t="inlineStr">
         <is>
           <t>NARESH KUMAR</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="66" t="inlineStr">
         <is>
           <t>9166233899</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" s="67" t="inlineStr">
         <is>
           <t>Madhyama Vashishth (8432571486)</t>
         </is>
       </c>
-      <c r="H30" s="7" t="n">
+      <c r="H30" s="68" t="n">
         <v>54</v>
       </c>
-      <c r="I30" s="7" t="n">
+      <c r="I30" s="68" t="n">
         <v>54</v>
       </c>
-      <c r="J30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="7" t="n">
+      <c r="J30" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="68" t="n">
         <v>38</v>
       </c>
-      <c r="L30" s="7" t="n">
+      <c r="L30" s="68" t="n">
         <v>38</v>
       </c>
-      <c r="M30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="7" t="n">
+      <c r="M30" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="68" t="n">
         <v>92</v>
       </c>
-      <c r="O30" s="7" t="n">
+      <c r="O30" s="68" t="n">
         <v>92</v>
       </c>
-      <c r="P30" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" s="9" t="inlineStr">
+      <c r="P30" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="66" t="n">
         <v>25</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="66" t="inlineStr">
         <is>
           <t>221773</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. करांटी (GOVT. SENIOR SECONDARY SCHOOL KARANTI)</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="67" t="inlineStr">
         <is>
           <t>PEEO KARATI</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="E31" s="67" t="inlineStr">
         <is>
           <t>DEEPAK SANWARIYA</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="66" t="inlineStr">
         <is>
           <t>9950736300</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G31" s="67" t="inlineStr">
         <is>
           <t>GHEESALAL GURJAR (9983507739)</t>
         </is>
       </c>
-      <c r="H31" s="7" t="n">
+      <c r="H31" s="68" t="n">
         <v>95</v>
       </c>
-      <c r="I31" s="7" t="n">
+      <c r="I31" s="68" t="n">
         <v>95</v>
       </c>
-      <c r="J31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="7" t="n">
+      <c r="J31" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="68" t="n">
         <v>49</v>
       </c>
-      <c r="L31" s="7" t="n">
+      <c r="L31" s="68" t="n">
         <v>49</v>
       </c>
-      <c r="M31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="7" t="n">
+      <c r="M31" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="68" t="n">
         <v>144</v>
       </c>
-      <c r="O31" s="7" t="n">
+      <c r="O31" s="68" t="n">
         <v>144</v>
       </c>
-      <c r="P31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="9" t="inlineStr">
+      <c r="P31" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="66" t="n">
         <v>26</v>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="66" t="inlineStr">
         <is>
           <t>221774</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. खेड़ी (GOVT. SENIOR SECONDARY SCHOOL KHEDI)</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="67" t="inlineStr">
         <is>
           <t>PEEO KARATI</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" s="67" t="inlineStr">
         <is>
           <t>SUSHAMA PANDEY</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" s="66" t="inlineStr">
         <is>
           <t>8107098772</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G32" s="67" t="inlineStr">
         <is>
           <t>SANDEEP BAGRANI (9602564649)</t>
         </is>
       </c>
-      <c r="H32" s="7" t="n">
+      <c r="H32" s="68" t="n">
         <v>44</v>
       </c>
-      <c r="I32" s="7" t="n">
+      <c r="I32" s="68" t="n">
         <v>44</v>
       </c>
-      <c r="J32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="7" t="n">
+      <c r="J32" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="68" t="n">
         <v>22</v>
       </c>
-      <c r="L32" s="7" t="n">
+      <c r="L32" s="68" t="n">
         <v>22</v>
       </c>
-      <c r="M32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="7" t="n">
+      <c r="M32" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="68" t="n">
         <v>66</v>
       </c>
-      <c r="O32" s="7" t="n">
+      <c r="O32" s="68" t="n">
         <v>66</v>
       </c>
-      <c r="P32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="9" t="inlineStr">
+      <c r="P32" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="66" t="n">
         <v>27</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="66" t="inlineStr">
         <is>
           <t>221777</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. कुम्हारिया (GOVT. SENIOR SECONDARY SCHOOL KUMHARIYA)</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="67" t="inlineStr">
         <is>
           <t>PEEO KUMHARIYA</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="67" t="inlineStr">
         <is>
           <t>JYOTI PRAKASH SHARMA</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="66" t="inlineStr">
         <is>
           <t>9460690289</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G33" s="67" t="inlineStr">
         <is>
           <t>Sheela chouhan (8619153192)</t>
         </is>
       </c>
-      <c r="H33" s="7" t="n">
+      <c r="H33" s="68" t="n">
         <v>94</v>
       </c>
-      <c r="I33" s="7" t="n">
+      <c r="I33" s="68" t="n">
         <v>94</v>
       </c>
-      <c r="J33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="7" t="n">
+      <c r="J33" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="68" t="n">
         <v>44</v>
       </c>
-      <c r="L33" s="7" t="n">
+      <c r="L33" s="68" t="n">
         <v>44</v>
       </c>
-      <c r="M33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="7" t="n">
+      <c r="M33" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="68" t="n">
         <v>138</v>
       </c>
-      <c r="O33" s="7" t="n">
+      <c r="O33" s="68" t="n">
         <v>138</v>
       </c>
-      <c r="P33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="9" t="inlineStr">
+      <c r="P33" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="66" t="n">
         <v>28</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="66" t="inlineStr">
         <is>
           <t>221757</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. कुरथल (GOVT. SENIOR SECONDARY SCHOOL KURTHAL)</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="67" t="inlineStr">
         <is>
           <t>PEEO NANDSI</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E34" s="67" t="inlineStr">
         <is>
           <t>BANNA LAL RAIGAR</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="66" t="inlineStr">
         <is>
           <t>9829157423</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G34" s="67" t="inlineStr">
         <is>
           <t>HARI SINGH MEENA (9414780660)</t>
         </is>
       </c>
-      <c r="H34" s="7" t="n">
+      <c r="H34" s="68" t="n">
         <v>47</v>
       </c>
-      <c r="I34" s="7" t="n">
+      <c r="I34" s="68" t="n">
         <v>47</v>
       </c>
-      <c r="J34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="7" t="n">
+      <c r="J34" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="68" t="n">
         <v>40</v>
       </c>
-      <c r="L34" s="7" t="n">
+      <c r="L34" s="68" t="n">
         <v>40</v>
       </c>
-      <c r="M34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="7" t="n">
+      <c r="M34" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="68" t="n">
         <v>87</v>
       </c>
-      <c r="O34" s="7" t="n">
+      <c r="O34" s="68" t="n">
         <v>87</v>
       </c>
-      <c r="P34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="9" t="inlineStr">
+      <c r="P34" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="66" t="n">
         <v>29</v>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="66" t="inlineStr">
         <is>
           <t>221759</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. लामगरा (GOVT. SENIOR SECONDARY SCHOOL LAMGARA)</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="67" t="inlineStr">
         <is>
           <t>PEEO LAMGARA</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="E35" s="67" t="inlineStr">
         <is>
           <t>RAJEEV KUMAR MANDOT</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F35" s="66" t="inlineStr">
         <is>
           <t>9413134849</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G35" s="67" t="inlineStr">
         <is>
           <t>HEMENDRA KUMAR TAILOR (9928305658)</t>
         </is>
       </c>
-      <c r="H35" s="7" t="n">
+      <c r="H35" s="68" t="n">
         <v>59</v>
       </c>
-      <c r="I35" s="7" t="n">
+      <c r="I35" s="68" t="n">
         <v>59</v>
       </c>
-      <c r="J35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="7" t="n">
+      <c r="J35" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="68" t="n">
         <v>36</v>
       </c>
-      <c r="L35" s="7" t="n">
+      <c r="L35" s="68" t="n">
         <v>36</v>
       </c>
-      <c r="M35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="7" t="n">
+      <c r="M35" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="68" t="n">
         <v>95</v>
       </c>
-      <c r="O35" s="7" t="n">
+      <c r="O35" s="68" t="n">
         <v>95</v>
       </c>
-      <c r="P35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="9" t="inlineStr">
+      <c r="P35" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="70" t="inlineStr">
         <is>
           <t>पूर्ण मिलान (Exact Match)</t>
         </is>
       </c>
     </row>
-    <row r="36" customFormat="1" s="47">
-      <c r="A36" s="42" t="n">
+    <row r="36">
+      <c r="A36" s="66" t="n">
         <v>30</v>
       </c>
-      <c r="B36" s="42" t="inlineStr">
+      <c r="B36" s="66" t="inlineStr">
         <is>
           <t>221772</t>
         </is>
       </c>
-      <c r="C36" s="43" t="inlineStr">
+      <c r="C36" s="67" t="inlineStr">
         <is>
           <t>रा.उ.मा.वि. नागोला (GOVT. SENIOR SECONDARY SCHOOL NAGOLA)</t>
         </is>
       </c>
-      <c r="D36" s="43" t="inlineStr">
+      <c r="D36" s="67" t="inlineStr">
         <is>
           <t>PEEO NAGOLA</t>
         </is>
       </c>
-      <c r="E36" s="43" t="inlineStr">
+      <c r="E36" s="67" t="inlineStr">
         <is>
           <t>VINOD KUMAR RAO</t>
         </is>
       </c>
-      <c r="F36" s="42" t="inlineStr">
+      <c r="F36" s="66" t="inlineStr">
         <is>
           <t>8955306674</t>
         </is>
       </c>
-      <c r="G36" s="43" t="inlineStr">
+      <c r="G36" s="67" t="inlineStr">
         <is>
           <t>MUKESH KUMAR RAWAT (9799203204)</t>
         </is>
       </c>
-      <c r="H36" s="44" t="n">
+      <c r="H36" s="68" t="n">
         <v>132</v>
       </c>
-      <c r="I36" s="44" t="n">
-        <v>133</v>
-      </c>
-      <c r="J36" s="45" t="n">
+      <c r="I36" s="68" t="n">
+        <v>132</v>
+      </c>
+      <c r="J36" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="68" t="n">
+        <v>90</v>
+      </c>
+      <c r="L36" s="68" t="n">
+        <v>90</v>
+      </c>
+      <c r="M36" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="68" t="n">
+        <v>222</v>
+      </c>
+      <c r="O36" s="68" t="n">
+        <v>222</v>
+      </c>
+      <c r="P36" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="66" t="n">
+        <v>31</v>
+      </c>
+      <c r="B37" s="66" t="inlineStr">
+        <is>
+          <t>221756</t>
+        </is>
+      </c>
+      <c r="C37" s="67" t="inlineStr">
+        <is>
+          <t>रा.उ.मा.वि. नांदसी (GOVT. SENIOR SECONDARY SCHOOL NANDSI)</t>
+        </is>
+      </c>
+      <c r="D37" s="67" t="inlineStr">
+        <is>
+          <t>PEEO NANDSI</t>
+        </is>
+      </c>
+      <c r="E37" s="67" t="inlineStr">
+        <is>
+          <t>OM PRAKASH VERMA</t>
+        </is>
+      </c>
+      <c r="F37" s="66" t="inlineStr">
+        <is>
+          <t>9001637473</t>
+        </is>
+      </c>
+      <c r="G37" s="67" t="inlineStr">
+        <is>
+          <t>SHANKAR LAL SAINI (8233686098)</t>
+        </is>
+      </c>
+      <c r="H37" s="68" t="n">
+        <v>55</v>
+      </c>
+      <c r="I37" s="68" t="n">
+        <v>55</v>
+      </c>
+      <c r="J37" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="68" t="n">
+        <v>37</v>
+      </c>
+      <c r="L37" s="68" t="n">
+        <v>37</v>
+      </c>
+      <c r="M37" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="68" t="n">
+        <v>92</v>
+      </c>
+      <c r="O37" s="68" t="n">
+        <v>92</v>
+      </c>
+      <c r="P37" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="66" t="n">
+        <v>32</v>
+      </c>
+      <c r="B38" s="66" t="inlineStr">
+        <is>
+          <t>401778</t>
+        </is>
+      </c>
+      <c r="C38" s="67" t="inlineStr">
+        <is>
+          <t>रा.उ.मा.वि. नेमेड़ा (GOVT. SENIOR SECONDARY SCHOOL NEMEDA)</t>
+        </is>
+      </c>
+      <c r="D38" s="67" t="inlineStr">
+        <is>
+          <t>PEEO KANAI KALAN</t>
+        </is>
+      </c>
+      <c r="E38" s="67" t="inlineStr">
+        <is>
+          <t>प्रभारी प्रधानाचार्य  Gourav Kumar (रा.उ.मा.वि. निमेड़ा)</t>
+        </is>
+      </c>
+      <c r="F38" s="66" t="inlineStr">
+        <is>
+          <t>9461249418</t>
+        </is>
+      </c>
+      <c r="G38" s="67" t="inlineStr">
+        <is>
+          <t>Dinesh sad (9928956796)</t>
+        </is>
+      </c>
+      <c r="H38" s="68" t="n">
+        <v>68</v>
+      </c>
+      <c r="I38" s="68" t="n">
+        <v>68</v>
+      </c>
+      <c r="J38" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="68" t="n">
+        <v>21</v>
+      </c>
+      <c r="L38" s="68" t="n">
+        <v>21</v>
+      </c>
+      <c r="M38" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="68" t="n">
+        <v>89</v>
+      </c>
+      <c r="O38" s="68" t="n">
+        <v>89</v>
+      </c>
+      <c r="P38" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="66" t="n">
+        <v>33</v>
+      </c>
+      <c r="B39" s="66" t="inlineStr">
+        <is>
+          <t>221761</t>
+        </is>
+      </c>
+      <c r="C39" s="67" t="inlineStr">
+        <is>
+          <t>रा.उ.मा.वि. निमेड़ा (GOVT. SENIOR SECONDARY SCHOOL NIMEDA)</t>
+        </is>
+      </c>
+      <c r="D39" s="67" t="inlineStr">
+        <is>
+          <t>PEEO LAMGARA</t>
+        </is>
+      </c>
+      <c r="E39" s="67" t="inlineStr">
+        <is>
+          <t>SUNITA SHARMA</t>
+        </is>
+      </c>
+      <c r="F39" s="66" t="inlineStr">
+        <is>
+          <t>9462905104</t>
+        </is>
+      </c>
+      <c r="G39" s="67" t="inlineStr">
+        <is>
+          <t>Puran Singh (8078654534)</t>
+        </is>
+      </c>
+      <c r="H39" s="68" t="n">
+        <v>55</v>
+      </c>
+      <c r="I39" s="68" t="n">
+        <v>50</v>
+      </c>
+      <c r="J39" s="71" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K39" s="68" t="n">
+        <v>37</v>
+      </c>
+      <c r="L39" s="68" t="n">
+        <v>37</v>
+      </c>
+      <c r="M39" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="68" t="n">
+        <v>92</v>
+      </c>
+      <c r="O39" s="68" t="n">
+        <v>87</v>
+      </c>
+      <c r="P39" s="71" t="n">
+        <v>-5</v>
+      </c>
+      <c r="Q39" s="72" t="inlineStr">
+        <is>
+          <t>अंतर: -5 (9-10 में -5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="66" t="n">
+        <v>34</v>
+      </c>
+      <c r="B40" s="66" t="inlineStr">
+        <is>
+          <t>221788</t>
+        </is>
+      </c>
+      <c r="C40" s="67" t="inlineStr">
+        <is>
+          <t>रा.उ.मा.वि. पाडंगा (GOVT. SENIOR SECONDARY SCHOOL PADANGA)</t>
+        </is>
+      </c>
+      <c r="D40" s="67" t="inlineStr">
+        <is>
+          <t>PEEO PADANGA</t>
+        </is>
+      </c>
+      <c r="E40" s="67" t="inlineStr">
+        <is>
+          <t>SMT ASHA RAJ</t>
+        </is>
+      </c>
+      <c r="F40" s="66" t="inlineStr">
+        <is>
+          <t>7877090975</t>
+        </is>
+      </c>
+      <c r="G40" s="67" t="inlineStr">
+        <is>
+          <t>Pankaj sharma (9413135717)</t>
+        </is>
+      </c>
+      <c r="H40" s="68" t="n">
+        <v>85</v>
+      </c>
+      <c r="I40" s="68" t="n">
+        <v>85</v>
+      </c>
+      <c r="J40" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="68" t="n">
+        <v>50</v>
+      </c>
+      <c r="L40" s="68" t="n">
+        <v>50</v>
+      </c>
+      <c r="M40" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="68" t="n">
+        <v>135</v>
+      </c>
+      <c r="O40" s="68" t="n">
+        <v>135</v>
+      </c>
+      <c r="P40" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="66" t="n">
+        <v>35</v>
+      </c>
+      <c r="B41" s="66" t="inlineStr">
+        <is>
+          <t>221766</t>
+        </is>
+      </c>
+      <c r="C41" s="67" t="inlineStr">
+        <is>
+          <t>रा.उ.मा.वि. पाडलिया (GOVT. SENIOR SECONDARY SCHOOL PADLIYA)</t>
+        </is>
+      </c>
+      <c r="D41" s="67" t="inlineStr">
+        <is>
+          <t>PEEO PADALIYA</t>
+        </is>
+      </c>
+      <c r="E41" s="67" t="inlineStr">
+        <is>
+          <t>LAXMI POPTANI</t>
+        </is>
+      </c>
+      <c r="F41" s="66" t="inlineStr">
+        <is>
+          <t>9549364023</t>
+        </is>
+      </c>
+      <c r="G41" s="67" t="inlineStr">
+        <is>
+          <t>HEMLATA SANKHLA (8233229902)</t>
+        </is>
+      </c>
+      <c r="H41" s="68" t="n">
+        <v>104</v>
+      </c>
+      <c r="I41" s="68" t="n">
+        <v>104</v>
+      </c>
+      <c r="J41" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="68" t="n">
+        <v>55</v>
+      </c>
+      <c r="L41" s="68" t="n">
+        <v>55</v>
+      </c>
+      <c r="M41" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="68" t="n">
+        <v>159</v>
+      </c>
+      <c r="O41" s="68" t="n">
+        <v>159</v>
+      </c>
+      <c r="P41" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="66" t="n">
+        <v>36</v>
+      </c>
+      <c r="B42" s="66" t="inlineStr">
+        <is>
+          <t>485033</t>
+        </is>
+      </c>
+      <c r="C42" s="67" t="inlineStr">
+        <is>
+          <t>रा.उ.मा.वि. पीपलिया (GOVT. SENIOR SECONDARY SCHOOL PIPLIYA)</t>
+        </is>
+      </c>
+      <c r="D42" s="67" t="inlineStr">
+        <is>
+          <t>PEEO BOOBKIYA</t>
+        </is>
+      </c>
+      <c r="E42" s="67" t="inlineStr">
+        <is>
+          <t>Vinod Kumar Meena</t>
+        </is>
+      </c>
+      <c r="F42" s="66" t="inlineStr">
+        <is>
+          <t>9828393814</t>
+        </is>
+      </c>
+      <c r="G42" s="67" t="inlineStr">
+        <is>
+          <t>Rakesh kumar meena (9928133088)</t>
+        </is>
+      </c>
+      <c r="H42" s="68" t="n">
+        <v>47</v>
+      </c>
+      <c r="I42" s="68" t="n">
+        <v>47</v>
+      </c>
+      <c r="J42" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="68" t="n">
+        <v>26</v>
+      </c>
+      <c r="L42" s="68" t="n">
+        <v>26</v>
+      </c>
+      <c r="M42" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="68" t="n">
+        <v>73</v>
+      </c>
+      <c r="O42" s="68" t="n">
+        <v>73</v>
+      </c>
+      <c r="P42" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="66" t="n">
+        <v>37</v>
+      </c>
+      <c r="B43" s="66" t="inlineStr">
+        <is>
+          <t>410677</t>
+        </is>
+      </c>
+      <c r="C43" s="67" t="inlineStr">
+        <is>
+          <t>रा.उ.मा.वि. रघुनाथगढ़ (GOVT. SENIOR SECONDARY SCHOOL RAGHUNATHGADH)</t>
+        </is>
+      </c>
+      <c r="D43" s="67" t="inlineStr">
+        <is>
+          <t>PEEO RAMMALIA</t>
+        </is>
+      </c>
+      <c r="E43" s="67" t="inlineStr">
+        <is>
+          <t>Lalit Kishore Sharma</t>
+        </is>
+      </c>
+      <c r="F43" s="66" t="inlineStr">
+        <is>
+          <t>8104466893</t>
+        </is>
+      </c>
+      <c r="G43" s="67" t="inlineStr">
+        <is>
+          <t>Shanti lal shadhu (8875076695)</t>
+        </is>
+      </c>
+      <c r="H43" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="66" t="n">
+        <v>38</v>
+      </c>
+      <c r="B44" s="66" t="inlineStr">
+        <is>
+          <t>221771</t>
+        </is>
+      </c>
+      <c r="C44" s="67" t="inlineStr">
+        <is>
+          <t>रा.उ.मा.वि. रेलवे कॉलोनी, बांदनवाड़ा (GOVT. SENIOR SECONDARY SCHOOL RAILWAY COLONY BANDANWARA)</t>
+        </is>
+      </c>
+      <c r="D44" s="67" t="inlineStr">
+        <is>
+          <t>PEEO BANDANWARA</t>
+        </is>
+      </c>
+      <c r="E44" s="67" t="inlineStr">
+        <is>
+          <t>DEVENDRA KUMAR SANKHLA</t>
+        </is>
+      </c>
+      <c r="F44" s="66" t="inlineStr">
+        <is>
+          <t>8949599466</t>
+        </is>
+      </c>
+      <c r="G44" s="67" t="inlineStr">
+        <is>
+          <t>MAMTA (8742094807)</t>
+        </is>
+      </c>
+      <c r="H44" s="68" t="n">
+        <v>95</v>
+      </c>
+      <c r="I44" s="68" t="n">
+        <v>95</v>
+      </c>
+      <c r="J44" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="68" t="n">
+        <v>77</v>
+      </c>
+      <c r="L44" s="68" t="n">
+        <v>77</v>
+      </c>
+      <c r="M44" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="68" t="n">
+        <v>172</v>
+      </c>
+      <c r="O44" s="68" t="n">
+        <v>172</v>
+      </c>
+      <c r="P44" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="66" t="n">
+        <v>39</v>
+      </c>
+      <c r="B45" s="66" t="inlineStr">
+        <is>
+          <t>221785</t>
+        </is>
+      </c>
+      <c r="C45" s="67" t="inlineStr">
+        <is>
+          <t>रा.उ.मा.वि. राममालिया (GOVT. SENIOR SECONDARY SCHOOL RAMMALIYA)</t>
+        </is>
+      </c>
+      <c r="D45" s="67" t="inlineStr">
+        <is>
+          <t>PEEO RAMMALIA</t>
+        </is>
+      </c>
+      <c r="E45" s="67" t="inlineStr">
+        <is>
+          <t>LAL CHAND MUNOTH</t>
+        </is>
+      </c>
+      <c r="F45" s="66" t="inlineStr">
+        <is>
+          <t>9928328808</t>
+        </is>
+      </c>
+      <c r="G45" s="67" t="inlineStr">
+        <is>
+          <t>Dilip Singh Rathore (9667718413)</t>
+        </is>
+      </c>
+      <c r="H45" s="68" t="n">
+        <v>73</v>
+      </c>
+      <c r="I45" s="68" t="n">
+        <v>73</v>
+      </c>
+      <c r="J45" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="68" t="n">
+        <v>42</v>
+      </c>
+      <c r="L45" s="68" t="n">
+        <v>42</v>
+      </c>
+      <c r="M45" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="68" t="n">
+        <v>115</v>
+      </c>
+      <c r="O45" s="68" t="n">
+        <v>115</v>
+      </c>
+      <c r="P45" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="66" t="n">
+        <v>40</v>
+      </c>
+      <c r="B46" s="66" t="inlineStr">
+        <is>
+          <t>221775</t>
+        </is>
+      </c>
+      <c r="C46" s="67" t="inlineStr">
+        <is>
+          <t>रा.उ.मा.वि. राताकोट (GOVT. SENIOR SECONDARY SCHOOL RATAKOT)</t>
+        </is>
+      </c>
+      <c r="D46" s="67" t="inlineStr">
+        <is>
+          <t>PEEO RATAKOT</t>
+        </is>
+      </c>
+      <c r="E46" s="67" t="inlineStr">
+        <is>
+          <t>KUNJ BIHARI SHARMA</t>
+        </is>
+      </c>
+      <c r="F46" s="66" t="inlineStr">
+        <is>
+          <t>9887753471</t>
+        </is>
+      </c>
+      <c r="G46" s="67" t="inlineStr">
+        <is>
+          <t>BALMUKUND JOSHI (9414283130)</t>
+        </is>
+      </c>
+      <c r="H46" s="68" t="n">
+        <v>70</v>
+      </c>
+      <c r="I46" s="68" t="n">
+        <v>70</v>
+      </c>
+      <c r="J46" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="68" t="n">
+        <v>52</v>
+      </c>
+      <c r="L46" s="68" t="n">
+        <v>52</v>
+      </c>
+      <c r="M46" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="68" t="n">
+        <v>122</v>
+      </c>
+      <c r="O46" s="68" t="n">
+        <v>122</v>
+      </c>
+      <c r="P46" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="66" t="n">
+        <v>41</v>
+      </c>
+      <c r="B47" s="66" t="inlineStr">
+        <is>
+          <t>410704</t>
+        </is>
+      </c>
+      <c r="C47" s="67" t="inlineStr">
+        <is>
+          <t>रा.उ.मा.वि. रूपपुरा (GOVT. SENIOR SECONDARY SCHOOL ROOPPURA)</t>
+        </is>
+      </c>
+      <c r="D47" s="67" t="inlineStr">
+        <is>
+          <t>PEEO DEVPURA</t>
+        </is>
+      </c>
+      <c r="E47" s="67" t="inlineStr">
+        <is>
+          <t>Mamta basur</t>
+        </is>
+      </c>
+      <c r="F47" s="66" t="inlineStr">
+        <is>
+          <t>7627050549</t>
+        </is>
+      </c>
+      <c r="G47" s="67" t="inlineStr">
+        <is>
+          <t>Kumawat Pratishtha (7725988808)</t>
+        </is>
+      </c>
+      <c r="H47" s="68" t="n">
+        <v>37</v>
+      </c>
+      <c r="I47" s="68" t="n">
+        <v>37</v>
+      </c>
+      <c r="J47" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="68" t="n">
+        <v>37</v>
+      </c>
+      <c r="O47" s="68" t="n">
+        <v>37</v>
+      </c>
+      <c r="P47" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="66" t="n">
+        <v>42</v>
+      </c>
+      <c r="B48" s="66" t="inlineStr">
+        <is>
+          <t>488946</t>
+        </is>
+      </c>
+      <c r="C48" s="67" t="inlineStr">
+        <is>
+          <t>रा.उ.मा.वि. सेदरिया (GOVT. SENIOR SECONDARY SCHOOL SEDRIYA)</t>
+        </is>
+      </c>
+      <c r="D48" s="67" t="inlineStr">
+        <is>
+          <t>PEEO CHHACHHUNDRA</t>
+        </is>
+      </c>
+      <c r="E48" s="67" t="inlineStr">
+        <is>
+          <t>RITU SHARMA</t>
+        </is>
+      </c>
+      <c r="F48" s="66" t="inlineStr">
+        <is>
+          <t>9829790044</t>
+        </is>
+      </c>
+      <c r="G48" s="67" t="inlineStr">
+        <is>
+          <t>Mukesh Chandra Gurjar (9413457331)</t>
+        </is>
+      </c>
+      <c r="H48" s="68" t="n">
+        <v>65</v>
+      </c>
+      <c r="I48" s="68" t="n">
+        <v>65</v>
+      </c>
+      <c r="J48" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="68" t="n">
+        <v>25</v>
+      </c>
+      <c r="L48" s="68" t="n">
+        <v>25</v>
+      </c>
+      <c r="M48" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="68" t="n">
+        <v>90</v>
+      </c>
+      <c r="O48" s="68" t="n">
+        <v>90</v>
+      </c>
+      <c r="P48" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="66" t="n">
+        <v>43</v>
+      </c>
+      <c r="B49" s="66" t="inlineStr">
+        <is>
+          <t>221781</t>
+        </is>
+      </c>
+      <c r="C49" s="67" t="inlineStr">
+        <is>
+          <t>रा.उ.मा.वि. सिंगावल (GOVT. SENIOR SECONDARY SCHOOL SINGAWAL)</t>
+        </is>
+      </c>
+      <c r="D49" s="67" t="inlineStr">
+        <is>
+          <t>PEEO SINGAWAL</t>
+        </is>
+      </c>
+      <c r="E49" s="67" t="inlineStr">
+        <is>
+          <t>SEEMA SHARMA</t>
+        </is>
+      </c>
+      <c r="F49" s="66" t="inlineStr">
+        <is>
+          <t>8290911983</t>
+        </is>
+      </c>
+      <c r="G49" s="67" t="inlineStr">
+        <is>
+          <t>LALIT KISHORE PAREEK (9414550520)</t>
+        </is>
+      </c>
+      <c r="H49" s="68" t="n">
+        <v>189</v>
+      </c>
+      <c r="I49" s="68" t="n">
+        <v>189</v>
+      </c>
+      <c r="J49" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="68" t="n">
+        <v>104</v>
+      </c>
+      <c r="L49" s="68" t="n">
+        <v>104</v>
+      </c>
+      <c r="M49" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="68" t="n">
+        <v>293</v>
+      </c>
+      <c r="O49" s="68" t="n">
+        <v>293</v>
+      </c>
+      <c r="P49" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="66" t="n">
+        <v>44</v>
+      </c>
+      <c r="B50" s="66" t="inlineStr">
+        <is>
+          <t>221782</t>
+        </is>
+      </c>
+      <c r="C50" s="67" t="inlineStr">
+        <is>
+          <t>रा.उ.मा.वि. सोबड़ी (GOVT. SENIOR SECONDARY SCHOOL SOBRI)</t>
+        </is>
+      </c>
+      <c r="D50" s="67" t="inlineStr">
+        <is>
+          <t>PEEO SOBRI</t>
+        </is>
+      </c>
+      <c r="E50" s="67" t="inlineStr">
+        <is>
+          <t>FAYYAZ MOHAMMED</t>
+        </is>
+      </c>
+      <c r="F50" s="66" t="inlineStr">
+        <is>
+          <t>9829487158</t>
+        </is>
+      </c>
+      <c r="G50" s="67" t="inlineStr">
+        <is>
+          <t>SHIVJI GURJAR (9166797832)</t>
+        </is>
+      </c>
+      <c r="H50" s="68" t="n">
+        <v>52</v>
+      </c>
+      <c r="I50" s="68" t="n">
+        <v>52</v>
+      </c>
+      <c r="J50" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="68" t="n">
+        <v>22</v>
+      </c>
+      <c r="L50" s="68" t="n">
+        <v>22</v>
+      </c>
+      <c r="M50" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="68" t="n">
+        <v>74</v>
+      </c>
+      <c r="O50" s="68" t="n">
+        <v>74</v>
+      </c>
+      <c r="P50" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="66" t="n">
+        <v>45</v>
+      </c>
+      <c r="B51" s="66" t="inlineStr">
+        <is>
+          <t>221770</t>
+        </is>
+      </c>
+      <c r="C51" s="67" t="inlineStr">
+        <is>
+          <t>महात्मा गांधी राजकीय विद्यालय, बांदनवाड़ा (MAHATMA GANDHI GOVT. SCHOOL BANDANWARA)</t>
+        </is>
+      </c>
+      <c r="D51" s="67" t="inlineStr">
+        <is>
+          <t>PEEO BANDANWARA</t>
+        </is>
+      </c>
+      <c r="E51" s="67" t="inlineStr">
+        <is>
+          <t>Afsar Ahmed</t>
+        </is>
+      </c>
+      <c r="F51" s="66" t="inlineStr">
+        <is>
+          <t>9079000589</t>
+        </is>
+      </c>
+      <c r="G51" s="67" t="inlineStr">
+        <is>
+          <t>Rajesh Kumar Rajput (7891997521)</t>
+        </is>
+      </c>
+      <c r="H51" s="68" t="n">
+        <v>41</v>
+      </c>
+      <c r="I51" s="68" t="n">
+        <v>41</v>
+      </c>
+      <c r="J51" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="68" t="n">
+        <v>41</v>
+      </c>
+      <c r="O51" s="68" t="n">
+        <v>41</v>
+      </c>
+      <c r="P51" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="66" t="n">
+        <v>46</v>
+      </c>
+      <c r="B52" s="66" t="inlineStr">
+        <is>
+          <t>221778</t>
+        </is>
+      </c>
+      <c r="C52" s="67" t="inlineStr">
+        <is>
+          <t>महात्मा गांधी राजकीय विद्यालय, भिनाय (MAHATMA GANDHI GOVT. SCHOOL BHINAI)</t>
+        </is>
+      </c>
+      <c r="D52" s="67" t="inlineStr">
+        <is>
+          <t>PEEO BHINAY</t>
+        </is>
+      </c>
+      <c r="E52" s="67" t="inlineStr">
+        <is>
+          <t>sanjeeda parveen</t>
+        </is>
+      </c>
+      <c r="F52" s="66" t="inlineStr">
+        <is>
+          <t>9468855086</t>
+        </is>
+      </c>
+      <c r="G52" s="67" t="inlineStr">
+        <is>
+          <t>महेश कुमार डाबी (7737343733)</t>
+        </is>
+      </c>
+      <c r="H52" s="68" t="n">
+        <v>44</v>
+      </c>
+      <c r="I52" s="68" t="n">
+        <v>44</v>
+      </c>
+      <c r="J52" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="68" t="n">
+        <v>42</v>
+      </c>
+      <c r="L52" s="68" t="n">
+        <v>42</v>
+      </c>
+      <c r="M52" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="68" t="n">
+        <v>86</v>
+      </c>
+      <c r="O52" s="68" t="n">
+        <v>86</v>
+      </c>
+      <c r="P52" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="66" t="n">
+        <v>47</v>
+      </c>
+      <c r="B53" s="66" t="inlineStr">
+        <is>
+          <t>221753</t>
+        </is>
+      </c>
+      <c r="C53" s="67" t="inlineStr">
+        <is>
+          <t>महात्मा गांधी राजकीय विद्यालय, देवलिया कलां (MAHATMA GANDHI GOVT. SCHOOL DEOLIYA KALAN)</t>
+        </is>
+      </c>
+      <c r="D53" s="67" t="inlineStr">
+        <is>
+          <t>PEEO DEOLIYA KALAN</t>
+        </is>
+      </c>
+      <c r="E53" s="67" t="inlineStr">
+        <is>
+          <t>RAKESH KUMAR BIRAWAT</t>
+        </is>
+      </c>
+      <c r="F53" s="66" t="inlineStr">
+        <is>
+          <t>9829835751</t>
+        </is>
+      </c>
+      <c r="G53" s="67" t="inlineStr">
+        <is>
+          <t>Basanti olaniya (7727945324)</t>
+        </is>
+      </c>
+      <c r="H53" s="68" t="n">
+        <v>70</v>
+      </c>
+      <c r="I53" s="68" t="n">
+        <v>70</v>
+      </c>
+      <c r="J53" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="68" t="n">
+        <v>40</v>
+      </c>
+      <c r="L53" s="68" t="n">
+        <v>40</v>
+      </c>
+      <c r="M53" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="68" t="n">
+        <v>110</v>
+      </c>
+      <c r="O53" s="68" t="n">
+        <v>110</v>
+      </c>
+      <c r="P53" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="66" t="n">
+        <v>48</v>
+      </c>
+      <c r="B54" s="66" t="inlineStr">
+        <is>
+          <t>485030</t>
+        </is>
+      </c>
+      <c r="C54" s="67" t="inlineStr">
+        <is>
+          <t>पीएम श्री रा.उ.मा.वि. बगराई (PM SHRI GOVT. SENIOR SECONDARY SCHOOL BAGRAI)</t>
+        </is>
+      </c>
+      <c r="D54" s="67" t="inlineStr">
+        <is>
+          <t>PEEO GURHA KHURD</t>
+        </is>
+      </c>
+      <c r="E54" s="67" t="inlineStr">
+        <is>
+          <t>श्री भूपेंद्र सिंह चारण (वरिष्ठ अध्यापक / संस्था प्रधान)</t>
+        </is>
+      </c>
+      <c r="F54" s="66" t="inlineStr">
+        <is>
+          <t>9929527319</t>
+        </is>
+      </c>
+      <c r="G54" s="67" t="inlineStr">
+        <is>
+          <t>DASHRATH BAIRWA (9116982528)</t>
+        </is>
+      </c>
+      <c r="H54" s="68" t="n">
+        <v>81</v>
+      </c>
+      <c r="I54" s="68" t="n">
+        <v>81</v>
+      </c>
+      <c r="J54" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="68" t="n">
+        <v>20</v>
+      </c>
+      <c r="L54" s="68" t="n">
+        <v>20</v>
+      </c>
+      <c r="M54" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="68" t="n">
+        <v>101</v>
+      </c>
+      <c r="O54" s="68" t="n">
+        <v>101</v>
+      </c>
+      <c r="P54" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="66" t="n">
+        <v>49</v>
+      </c>
+      <c r="B55" s="66" t="inlineStr">
+        <is>
+          <t>221754</t>
+        </is>
+      </c>
+      <c r="C55" s="67" t="inlineStr">
+        <is>
+          <t>पीएम श्री रा.उ.मा.वि. देवलिया कलां (PM SHRI GOVT. SENIOR SECONDARY SCHOOL DEOLIYA KALAN)</t>
+        </is>
+      </c>
+      <c r="D55" s="67" t="inlineStr">
+        <is>
+          <t>PEEO DEOLIYA KALAN</t>
+        </is>
+      </c>
+      <c r="E55" s="67" t="inlineStr">
+        <is>
+          <t>PURNIMA</t>
+        </is>
+      </c>
+      <c r="F55" s="66" t="inlineStr">
+        <is>
+          <t>9414343109</t>
+        </is>
+      </c>
+      <c r="G55" s="67" t="inlineStr">
+        <is>
+          <t>shahrukh khan (7976098421)</t>
+        </is>
+      </c>
+      <c r="H55" s="68" t="n">
+        <v>284</v>
+      </c>
+      <c r="I55" s="68" t="n">
+        <v>284</v>
+      </c>
+      <c r="J55" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="68" t="n">
+        <v>242</v>
+      </c>
+      <c r="L55" s="68" t="n">
+        <v>242</v>
+      </c>
+      <c r="M55" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="68" t="n">
+        <v>526</v>
+      </c>
+      <c r="O55" s="68" t="n">
+        <v>526</v>
+      </c>
+      <c r="P55" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="70" t="inlineStr">
+        <is>
+          <t>पूर्ण मिलान (Exact Match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="24" customHeight="1" s="26">
+      <c r="A56" s="73" t="inlineStr">
+        <is>
+          <t>कुल राजकीय विद्यालय योग (49 Schools Total)</t>
+        </is>
+      </c>
+      <c r="B56" s="74" t="n"/>
+      <c r="C56" s="74" t="n"/>
+      <c r="D56" s="74" t="n"/>
+      <c r="E56" s="74" t="n"/>
+      <c r="F56" s="74" t="n"/>
+      <c r="G56" s="74" t="n"/>
+      <c r="H56" s="75" t="n">
+        <v>4057</v>
+      </c>
+      <c r="I56" s="75" t="n">
+        <v>4062</v>
+      </c>
+      <c r="J56" s="76" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" s="75" t="n">
+        <v>2395</v>
+      </c>
+      <c r="L56" s="75" t="n">
+        <v>2396</v>
+      </c>
+      <c r="M56" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="K36" s="44" t="n">
-        <v>90</v>
-      </c>
-      <c r="L36" s="44" t="n">
-        <v>90</v>
-      </c>
-      <c r="M36" s="48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="44" t="n">
-        <v>222</v>
-      </c>
-      <c r="O36" s="44" t="n">
-        <v>223</v>
-      </c>
-      <c r="P36" s="45" t="n">
+      <c r="N56" s="75" t="n">
+        <v>6452</v>
+      </c>
+      <c r="O56" s="75" t="n">
+        <v>6458</v>
+      </c>
+      <c r="P56" s="76" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q56" s="77" t="inlineStr">
+        <is>
+          <t>कुल अंतर: +6 (3 विद्यालयों में अंतर, 46 में पूर्ण मिलान)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1" s="26">
+      <c r="A58" s="78" t="inlineStr">
+        <is>
+          <t>भाग - 2 : गैर-सरकारी / निजी विद्यालय (8 विद्यालय) - केवल समान परीक्षा पोर्टल पर दर्ज मांग व संस्था प्रधान विवरण</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1" s="26">
+      <c r="A59" s="79" t="inlineStr">
+        <is>
+          <t>* नोट: ये 8 निजी विद्यालय समान परीक्षा 2026-27 में शामिल हैं, किंतु 'school enrolment.xlsx' (राजकीय शाला दर्पण नामांकन) में नहीं हैं।</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1" s="26">
+      <c r="A60" s="80" t="inlineStr">
+        <is>
+          <t>क्र.सं.</t>
+        </is>
+      </c>
+      <c r="B60" s="80" t="inlineStr">
+        <is>
+          <t>विद्यालय कोड</t>
+        </is>
+      </c>
+      <c r="C60" s="80" t="inlineStr">
+        <is>
+          <t>निजी विद्यालय का नाम (School Name)</t>
+        </is>
+      </c>
+      <c r="D60" s="80" t="inlineStr">
+        <is>
+          <t>संबद्ध PEEO</t>
+        </is>
+      </c>
+      <c r="E60" s="80" t="inlineStr">
+        <is>
+          <t>संस्था प्रधान (Principal)</t>
+        </is>
+      </c>
+      <c r="F60" s="80" t="inlineStr">
+        <is>
+          <t>संस्था प्रधान मोबाइल</t>
+        </is>
+      </c>
+      <c r="G60" s="80" t="inlineStr">
+        <is>
+          <t>परीक्षा प्रभारी संपर्क</t>
+        </is>
+      </c>
+      <c r="H60" s="80" t="inlineStr">
+        <is>
+          <t>नामांकन (9-10)</t>
+        </is>
+      </c>
+      <c r="I60" s="80" t="inlineStr">
+        <is>
+          <t>समान परीक्षा (9+10)</t>
+        </is>
+      </c>
+      <c r="J60" s="80" t="inlineStr">
+        <is>
+          <t>अंतर</t>
+        </is>
+      </c>
+      <c r="K60" s="80" t="inlineStr">
+        <is>
+          <t>नामांकन (11-12)</t>
+        </is>
+      </c>
+      <c r="L60" s="80" t="inlineStr">
+        <is>
+          <t>समान परीक्षा (11+12)</t>
+        </is>
+      </c>
+      <c r="M60" s="80" t="inlineStr">
+        <is>
+          <t>अंतर</t>
+        </is>
+      </c>
+      <c r="N60" s="80" t="inlineStr">
+        <is>
+          <t>कुल नामांकन</t>
+        </is>
+      </c>
+      <c r="O60" s="80" t="inlineStr">
+        <is>
+          <t>समान परीक्षा कुल मांग</t>
+        </is>
+      </c>
+      <c r="P60" s="80" t="inlineStr">
+        <is>
+          <t>अंतर</t>
+        </is>
+      </c>
+      <c r="Q60" s="80" t="inlineStr">
+        <is>
+          <t>स्थिति / टिप्पणी</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="81" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="46" t="inlineStr">
-        <is>
-          <t>अंतर: +1 (9-10 में +1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>221756</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>रा.उ.मा.वि. नांदसी (GOVT. SENIOR SECONDARY SCHOOL NANDSI)</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>PEEO NANDSI</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>OM PRAKASH VERMA</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>9001637473</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>SHANKAR LAL SAINI (8233686098)</t>
-        </is>
-      </c>
-      <c r="H37" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="I37" s="7" t="n">
-        <v>59</v>
-      </c>
-      <c r="J37" s="10" t="n">
+      <c r="B61" s="81" t="inlineStr">
+        <is>
+          <t>P16099</t>
+        </is>
+      </c>
+      <c r="C61" s="82" t="inlineStr">
+        <is>
+          <t>GURUKUL KESARI PUBLIC SECONDARY SCHOOL BANDANWARA</t>
+        </is>
+      </c>
+      <c r="D61" s="82" t="inlineStr">
+        <is>
+          <t>PEEO BANDANWARA</t>
+        </is>
+      </c>
+      <c r="E61" s="82" t="inlineStr">
+        <is>
+          <t>SANWAR SINGH</t>
+        </is>
+      </c>
+      <c r="F61" s="81" t="inlineStr">
+        <is>
+          <t>9829395917</t>
+        </is>
+      </c>
+      <c r="G61" s="82" t="inlineStr">
+        <is>
+          <t>NAVEEN KUMAR (9119395917)</t>
+        </is>
+      </c>
+      <c r="H61" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" s="69" t="n">
+        <v>483</v>
+      </c>
+      <c r="J61" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="69" t="n">
+        <v>458</v>
+      </c>
+      <c r="M61" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O61" s="69" t="n">
+        <v>941</v>
+      </c>
+      <c r="P61" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q61" s="82" t="inlineStr">
+        <is>
+          <t>निजी विद्यालय (समान परीक्षा मांग दर्ज)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="B62" s="81" t="inlineStr">
+        <is>
+          <t>P16865</t>
+        </is>
+      </c>
+      <c r="C62" s="82" t="inlineStr">
+        <is>
+          <t>SUMER SENIOR SECONDARY SCHOOL BHINAI</t>
+        </is>
+      </c>
+      <c r="D62" s="82" t="inlineStr">
+        <is>
+          <t>PEEO BHINAY</t>
+        </is>
+      </c>
+      <c r="E62" s="82" t="inlineStr">
+        <is>
+          <t>Manisha</t>
+        </is>
+      </c>
+      <c r="F62" s="81" t="inlineStr">
+        <is>
+          <t>8078661911</t>
+        </is>
+      </c>
+      <c r="G62" s="82" t="inlineStr">
+        <is>
+          <t>Muntazim Khan (9460609888)</t>
+        </is>
+      </c>
+      <c r="H62" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" s="69" t="n">
+        <v>51</v>
+      </c>
+      <c r="J62" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="69" t="n">
+        <v>12</v>
+      </c>
+      <c r="M62" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O62" s="69" t="n">
+        <v>63</v>
+      </c>
+      <c r="P62" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q62" s="82" t="inlineStr">
+        <is>
+          <t>निजी विद्यालय (समान परीक्षा मांग दर्ज)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="B63" s="81" t="inlineStr">
+        <is>
+          <t>P16964</t>
+        </is>
+      </c>
+      <c r="C63" s="82" t="inlineStr">
+        <is>
+          <t>SAMRAT INTERNATIONAL SCHOOL BANDANWARA</t>
+        </is>
+      </c>
+      <c r="D63" s="82" t="inlineStr">
+        <is>
+          <t>PEEO BANDANWARA</t>
+        </is>
+      </c>
+      <c r="E63" s="82" t="inlineStr">
+        <is>
+          <t>Kamlesh Kumar sharma</t>
+        </is>
+      </c>
+      <c r="F63" s="81" t="inlineStr">
+        <is>
+          <t>9950000855</t>
+        </is>
+      </c>
+      <c r="G63" s="82" t="inlineStr">
+        <is>
+          <t>Jitendra prajapat (9983606823)</t>
+        </is>
+      </c>
+      <c r="H63" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" s="69" t="n">
+        <v>112</v>
+      </c>
+      <c r="J63" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O63" s="69" t="n">
+        <v>112</v>
+      </c>
+      <c r="P63" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q63" s="82" t="inlineStr">
+        <is>
+          <t>निजी विद्यालय (समान परीक्षा मांग दर्ज)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="81" t="n">
         <v>4</v>
       </c>
-      <c r="K37" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="L37" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="M37" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N37" s="7" t="n">
+      <c r="B64" s="81" t="inlineStr">
+        <is>
+          <t>P16968</t>
+        </is>
+      </c>
+      <c r="C64" s="82" t="inlineStr">
+        <is>
+          <t>DRONA CHARYA SECONDARY SCHOOL BHINAI</t>
+        </is>
+      </c>
+      <c r="D64" s="82" t="inlineStr">
+        <is>
+          <t>PEEO BHINAY</t>
+        </is>
+      </c>
+      <c r="E64" s="82" t="inlineStr">
+        <is>
+          <t>Dronacharya secondary school bhinai</t>
+        </is>
+      </c>
+      <c r="F64" s="81" t="inlineStr">
+        <is>
+          <t>9252971704</t>
+        </is>
+      </c>
+      <c r="G64" s="82" t="inlineStr">
+        <is>
+          <t>Abdul mukaddas (9602560794)</t>
+        </is>
+      </c>
+      <c r="H64" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I64" s="69" t="n">
+        <v>12</v>
+      </c>
+      <c r="J64" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O64" s="69" t="n">
+        <v>12</v>
+      </c>
+      <c r="P64" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q64" s="82" t="inlineStr">
+        <is>
+          <t>निजी विद्यालय (समान परीक्षा मांग दर्ज)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="81" t="n">
+        <v>5</v>
+      </c>
+      <c r="B65" s="81" t="inlineStr">
+        <is>
+          <t>P19054</t>
+        </is>
+      </c>
+      <c r="C65" s="82" t="inlineStr">
+        <is>
+          <t>SIDDHARTH INTERNATIONAL SCHOOL BANDANWARA</t>
+        </is>
+      </c>
+      <c r="D65" s="82" t="inlineStr">
+        <is>
+          <t>PEEO BANDANWARA</t>
+        </is>
+      </c>
+      <c r="E65" s="82" t="inlineStr">
+        <is>
+          <t>KAILASH RAWAT</t>
+        </is>
+      </c>
+      <c r="F65" s="81" t="inlineStr">
+        <is>
+          <t>9784505003</t>
+        </is>
+      </c>
+      <c r="G65" s="82" t="inlineStr">
+        <is>
+          <t>NARENDRA SEN (8107179458)</t>
+        </is>
+      </c>
+      <c r="H65" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I65" s="69" t="n">
+        <v>159</v>
+      </c>
+      <c r="J65" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O65" s="69" t="n">
+        <v>159</v>
+      </c>
+      <c r="P65" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q65" s="82" t="inlineStr">
+        <is>
+          <t>निजी विद्यालय (समान परीक्षा मांग दर्ज)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="81" t="n">
+        <v>6</v>
+      </c>
+      <c r="B66" s="81" t="inlineStr">
+        <is>
+          <t>P19678</t>
+        </is>
+      </c>
+      <c r="C66" s="82" t="inlineStr">
+        <is>
+          <t>SUN RISE CONVENT SCHOOL BHINAI</t>
+        </is>
+      </c>
+      <c r="D66" s="82" t="inlineStr">
+        <is>
+          <t>PEEO BHINAY</t>
+        </is>
+      </c>
+      <c r="E66" s="82" t="inlineStr">
+        <is>
+          <t>SHIVPAL SINGH RATHORE</t>
+        </is>
+      </c>
+      <c r="F66" s="81" t="inlineStr">
+        <is>
+          <t>9413202086</t>
+        </is>
+      </c>
+      <c r="G66" s="82" t="inlineStr">
+        <is>
+          <t>MOHD SHAKEEL DESHWALI (9636239392)</t>
+        </is>
+      </c>
+      <c r="H66" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I66" s="69" t="n">
+        <v>72</v>
+      </c>
+      <c r="J66" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O66" s="69" t="n">
+        <v>72</v>
+      </c>
+      <c r="P66" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q66" s="82" t="inlineStr">
+        <is>
+          <t>निजी विद्यालय (समान परीक्षा मांग दर्ज)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="81" t="n">
+        <v>7</v>
+      </c>
+      <c r="B67" s="81" t="inlineStr">
+        <is>
+          <t>P48759</t>
+        </is>
+      </c>
+      <c r="C67" s="82" t="inlineStr">
+        <is>
+          <t>KUCHAMAN SHIKSHAN SANSTHAN BANDANWARA</t>
+        </is>
+      </c>
+      <c r="D67" s="82" t="inlineStr">
+        <is>
+          <t>PEEO BANDANWARA</t>
+        </is>
+      </c>
+      <c r="E67" s="82" t="inlineStr">
+        <is>
+          <t>RAJENDRA PRASAD VAISHNAV</t>
+        </is>
+      </c>
+      <c r="F67" s="81" t="inlineStr">
+        <is>
+          <t>7877235353</t>
+        </is>
+      </c>
+      <c r="G67" s="82" t="inlineStr">
+        <is>
+          <t>DEVILAL JAT (8949427280)</t>
+        </is>
+      </c>
+      <c r="H67" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I67" s="69" t="n">
+        <v>315</v>
+      </c>
+      <c r="J67" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="69" t="n">
+        <v>183</v>
+      </c>
+      <c r="M67" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O67" s="69" t="n">
+        <v>498</v>
+      </c>
+      <c r="P67" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q67" s="82" t="inlineStr">
+        <is>
+          <t>निजी विद्यालय (समान परीक्षा मांग दर्ज)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="81" t="n">
+        <v>8</v>
+      </c>
+      <c r="B68" s="81" t="inlineStr">
+        <is>
+          <t>P55700</t>
+        </is>
+      </c>
+      <c r="C68" s="82" t="inlineStr">
+        <is>
+          <t>TAGORE GLOBAL SCHOOL (EKALSINGHA)</t>
+        </is>
+      </c>
+      <c r="D68" s="82" t="inlineStr">
+        <is>
+          <t>PEEO EKALSEENGA</t>
+        </is>
+      </c>
+      <c r="E68" s="82" t="inlineStr">
+        <is>
+          <t>AALOK MISHRA</t>
+        </is>
+      </c>
+      <c r="F68" s="81" t="inlineStr">
+        <is>
+          <t>9251300400</t>
+        </is>
+      </c>
+      <c r="G68" s="82" t="inlineStr">
+        <is>
+          <t>RAVI SHANKAR SHARMA (8504872321)</t>
+        </is>
+      </c>
+      <c r="H68" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I68" s="69" t="n">
         <v>92</v>
       </c>
-      <c r="O37" s="7" t="n">
-        <v>98</v>
-      </c>
-      <c r="P37" s="10" t="n">
+      <c r="J68" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O68" s="69" t="n">
+        <v>92</v>
+      </c>
+      <c r="P68" s="81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q68" s="82" t="inlineStr">
+        <is>
+          <t>निजी विद्यालय (समान परीक्षा मांग दर्ज)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="24" customHeight="1" s="26">
+      <c r="A69" s="83" t="inlineStr">
+        <is>
+          <t>कुल निजी विद्यालय योग (8 Private Schools Total)</t>
+        </is>
+      </c>
+      <c r="B69" s="84" t="n"/>
+      <c r="C69" s="84" t="n"/>
+      <c r="D69" s="84" t="n"/>
+      <c r="E69" s="84" t="n"/>
+      <c r="F69" s="84" t="n"/>
+      <c r="G69" s="84" t="n"/>
+      <c r="H69" s="83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I69" s="85" t="n">
+        <v>1296</v>
+      </c>
+      <c r="J69" s="83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="85" t="n">
+        <v>653</v>
+      </c>
+      <c r="M69" s="83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O69" s="85" t="n">
+        <v>1949</v>
+      </c>
+      <c r="P69" s="83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q69" s="86" t="inlineStr">
+        <is>
+          <t>कुल निजी मांग: 1949</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="24" customHeight="1" s="26">
+      <c r="A71" s="87" t="inlineStr">
+        <is>
+          <t>महायोग (GRAND TOTAL: ब्लॉक भिनाय - कुल 57 विद्यालय)</t>
+        </is>
+      </c>
+      <c r="B71" s="88" t="n"/>
+      <c r="C71" s="88" t="n"/>
+      <c r="D71" s="88" t="n"/>
+      <c r="E71" s="88" t="n"/>
+      <c r="F71" s="88" t="n"/>
+      <c r="G71" s="88" t="n"/>
+      <c r="H71" s="89" t="n">
+        <v>4057</v>
+      </c>
+      <c r="I71" s="89" t="n">
+        <v>5358</v>
+      </c>
+      <c r="J71" s="89" t="n">
+        <v>5</v>
+      </c>
+      <c r="K71" s="89" t="n">
+        <v>2395</v>
+      </c>
+      <c r="L71" s="89" t="n">
+        <v>3049</v>
+      </c>
+      <c r="M71" s="89" t="n">
+        <v>1</v>
+      </c>
+      <c r="N71" s="89" t="n">
+        <v>6452</v>
+      </c>
+      <c r="O71" s="89" t="n">
+        <v>8407</v>
+      </c>
+      <c r="P71" s="89" t="n">
         <v>6</v>
       </c>
-      <c r="Q37" s="11" t="inlineStr">
-        <is>
-          <t>अंतर: +6 (9-10 में +4, 11-12 में +2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>401778</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>रा.उ.मा.वि. नेमेड़ा (GOVT. SENIOR SECONDARY SCHOOL NEMEDA)</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>PEEO KANAI KALAN</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>प्रभारी प्रधानाचार्य  Gourav Kumar (रा.उ.मा.वि. निमेड़ा)</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>9461249418</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>Dinesh sad (9928956796)</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="n">
-        <v>68</v>
-      </c>
-      <c r="I38" s="7" t="n">
-        <v>68</v>
-      </c>
-      <c r="J38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="L38" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="7" t="n">
-        <v>89</v>
-      </c>
-      <c r="O38" s="7" t="n">
-        <v>89</v>
-      </c>
-      <c r="P38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="9" t="inlineStr">
-        <is>
-          <t>पूर्ण मिलान (Exact Match)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>221761</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>रा.उ.मा.वि. निमेड़ा (GOVT. SENIOR SECONDARY SCHOOL NIMEDA)</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>PEEO LAMGARA</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>SUNITA SHARMA</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>9462905104</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>Puran Singh (8078654534)</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="I39" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="J39" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="L39" s="7" t="n">
-        <v>39</v>
-      </c>
-      <c r="M39" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N39" s="7" t="n">
-        <v>92</v>
-      </c>
-      <c r="O39" s="7" t="n">
-        <v>94</v>
-      </c>
-      <c r="P39" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q39" s="11" t="inlineStr">
-        <is>
-          <t>अंतर: +2 (11-12 में +2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>221788</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>रा.उ.मा.वि. पाडंगा (GOVT. SENIOR SECONDARY SCHOOL PADANGA)</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>PEEO PADANGA</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>SMT ASHA RAJ</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>7877090975</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>Pankaj sharma (9413135717)</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="n">
-        <v>85</v>
-      </c>
-      <c r="I40" s="7" t="n">
-        <v>85</v>
-      </c>
-      <c r="J40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="L40" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="7" t="n">
-        <v>135</v>
-      </c>
-      <c r="O40" s="7" t="n">
-        <v>135</v>
-      </c>
-      <c r="P40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="9" t="inlineStr">
-        <is>
-          <t>पूर्ण मिलान (Exact Match)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>221766</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>रा.उ.मा.वि. पाडलिया (GOVT. SENIOR SECONDARY SCHOOL PADLIYA)</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>PEEO PADALIYA</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>LAXMI POPTANI</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>9549364023</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr">
-        <is>
-          <t>HEMLATA SANKHLA (8233229902)</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="n">
-        <v>104</v>
-      </c>
-      <c r="I41" s="7" t="n">
-        <v>104</v>
-      </c>
-      <c r="J41" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="L41" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="M41" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="7" t="n">
-        <v>159</v>
-      </c>
-      <c r="O41" s="7" t="n">
-        <v>159</v>
-      </c>
-      <c r="P41" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="9" t="inlineStr">
-        <is>
-          <t>पूर्ण मिलान (Exact Match)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>485033</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>रा.उ.मा.वि. पीपलिया (GOVT. SENIOR SECONDARY SCHOOL PIPLIYA)</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>PEEO BOOBKIYA</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>Vinod Kumar Meena</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>9828393814</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>Rakesh kumar meena (9928133088)</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="I42" s="7" t="n">
-        <v>47</v>
-      </c>
-      <c r="J42" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="L42" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="O42" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="P42" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="9" t="inlineStr">
-        <is>
-          <t>पूर्ण मिलान (Exact Match)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>410677</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>रा.उ.मा.वि. रघुनाथगढ़ (GOVT. SENIOR SECONDARY SCHOOL RAGHUNATHGADH)</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>PEEO RAMMALIA</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>Lalit Kishore Sharma</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>8104466893</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>Shanti lal shadhu (8875076695)</t>
-        </is>
-      </c>
-      <c r="H43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="9" t="inlineStr">
-        <is>
-          <t>पूर्ण मिलान (Exact Match)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>221771</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>रा.उ.मा.वि. रेलवे कॉलोनी, बांदनवाड़ा (GOVT. SENIOR SECONDARY SCHOOL RAILWAY COLONY BANDANWARA)</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>PEEO BANDANWARA</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>DEVENDRA KUMAR SANKHLA</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>8949599466</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>MAMTA (8742094807)</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="I44" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="J44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>77</v>
-      </c>
-      <c r="L44" s="7" t="n">
-        <v>77</v>
-      </c>
-      <c r="M44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="7" t="n">
-        <v>172</v>
-      </c>
-      <c r="O44" s="7" t="n">
-        <v>172</v>
-      </c>
-      <c r="P44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="9" t="inlineStr">
-        <is>
-          <t>पूर्ण मिलान (Exact Match)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>221785</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>रा.उ.मा.वि. राममालिया (GOVT. SENIOR SECONDARY SCHOOL RAMMALIYA)</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>PEEO RAMMALIA</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>LAL CHAND MUNOTH</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>9928328808</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="inlineStr">
-        <is>
-          <t>Dilip Singh Rathore (9667718413)</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="I45" s="7" t="n">
-        <v>73</v>
-      </c>
-      <c r="J45" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="L45" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="M45" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="7" t="n">
-        <v>115</v>
-      </c>
-      <c r="O45" s="7" t="n">
-        <v>115</v>
-      </c>
-      <c r="P45" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="9" t="inlineStr">
-        <is>
-          <t>पूर्ण मिलान (Exact Match)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>221775</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>रा.उ.मा.वि. राताकोट (GOVT. SENIOR SECONDARY SCHOOL RATAKOT)</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>PEEO RATAKOT</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>KUNJ BIHARI SHARMA</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>9887753471</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>BALMUKUND JOSHI (9414283130)</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="I46" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="J46" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="L46" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="M46" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="7" t="n">
-        <v>122</v>
-      </c>
-      <c r="O46" s="7" t="n">
-        <v>122</v>
-      </c>
-      <c r="P46" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="9" t="inlineStr">
-        <is>
-          <t>पूर्ण मिलान (Exact Match)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>410704</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>रा.उ.मा.वि. रूपपुरा (GOVT. SENIOR SECONDARY SCHOOL ROOPPURA)</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>PEEO DEVPURA</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>Mamta basur</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>7627050549</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>Kumawat Pratishtha (7725988808)</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="I47" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="J47" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="O47" s="7" t="n">
-        <v>37</v>
-      </c>
-      <c r="P47" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="9" t="inlineStr">
-        <is>
-          <t>पूर्ण मिलान (Exact Match)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>488946</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>रा.उ.मा.वि. सेदरिया (GOVT. SENIOR SECONDARY SCHOOL SEDRIYA)</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>PEEO CHHACHHUNDRA</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>RITU SHARMA</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>9829790044</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>Mukesh Chandra Gurjar (9413457331)</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="I48" s="7" t="n">
-        <v>65</v>
-      </c>
-      <c r="J48" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="L48" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="M48" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="7" t="n">
-        <v>90</v>
-      </c>
-      <c r="O48" s="7" t="n">
-        <v>90</v>
-      </c>
-      <c r="P48" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="9" t="inlineStr">
-        <is>
-          <t>पूर्ण मिलान (Exact Match)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>221781</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>रा.उ.मा.वि. सिंगावल (GOVT. SENIOR SECONDARY SCHOOL SINGAWAL)</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>PEEO SINGAWAL</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>SEEMA SHARMA</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>8290911983</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>LALIT KISHORE PAREEK (9414550520)</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="n">
-        <v>189</v>
-      </c>
-      <c r="I49" s="7" t="n">
-        <v>189</v>
-      </c>
-      <c r="J49" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>104</v>
-      </c>
-      <c r="L49" s="7" t="n">
-        <v>104</v>
-      </c>
-      <c r="M49" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="7" t="n">
-        <v>293</v>
-      </c>
-      <c r="O49" s="7" t="n">
-        <v>293</v>
-      </c>
-      <c r="P49" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="9" t="inlineStr">
-        <is>
-          <t>पूर्ण मिलान (Exact Match)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>221782</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>रा.उ.मा.वि. सोबड़ी (GOVT. SENIOR SECONDARY SCHOOL SOBRI)</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>PEEO SOBRI</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>FAYYAZ MOHAMMED</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>9829487158</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>SHIVJI GURJAR (9166797832)</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="I50" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="J50" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="L50" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="M50" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="7" t="n">
-        <v>74</v>
-      </c>
-      <c r="O50" s="7" t="n">
-        <v>74</v>
-      </c>
-      <c r="P50" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="9" t="inlineStr">
-        <is>
-          <t>पूर्ण मिलान (Exact Match)</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>221770</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>महात्मा गांधी राजकीय विद्यालय, बांदनवाड़ा (MAHATMA GANDHI GOVT. SCHOOL BANDANWARA)</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>PEEO BANDANWARA</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>Afsar Ahmed</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>9079000589</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>Rajesh Kumar Rajput (7891997521)</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="I51" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="J51" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="O51" s="7" t="n">
-        <v>41</v>
-      </c>
-      <c r="P51" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="9" t="inlineStr">
-        <is>
-          <t>पूर्ण मिलान (Exact Match)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>221778</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>महात्मा गांधी राजकीय विद्यालय, भिनाय (MAHATMA GANDHI GOVT. SCHOOL BHINAI)</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>PEEO BHINAY</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>sanjeeda parveen</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>9468855086</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>महेश कुमार डाबी (7737343733)</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="I52" s="7" t="n">
-        <v>44</v>
-      </c>
-      <c r="J52" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>42</v>
-      </c>
-      <c r="L52" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="M52" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N52" s="7" t="n">
-        <v>86</v>
-      </c>
-      <c r="O52" s="7" t="n">
-        <v>87</v>
-      </c>
-      <c r="P52" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q52" s="11" t="inlineStr">
-        <is>
-          <t>अंतर: +1 (11-12 में +1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>221753</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>महात्मा गांधी राजकीय विद्यालय, देवलिया कलां (MAHATMA GANDHI GOVT. SCHOOL DEOLIYA KALAN)</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>PEEO DEOLIYA KALAN</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>RAKESH KUMAR BIRAWAT</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>9829835751</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>Basanti olaniya (7727945324)</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="I53" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="J53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="L53" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="M53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="7" t="n">
-        <v>110</v>
-      </c>
-      <c r="O53" s="7" t="n">
-        <v>110</v>
-      </c>
-      <c r="P53" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="9" t="inlineStr">
-        <is>
-          <t>पूर्ण मिलान (Exact Match)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>485030</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>पीएम श्री रा.उ.मा.वि. बगराई (PM SHRI GOVT. SENIOR SECONDARY SCHOOL BAGRAI)</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>PEEO GURHA KHURD</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>श्री भूपेंद्र सिंह चारण (वरिष्ठ अध्यापक / संस्था प्रधान)</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>9929527319</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>DASHRATH BAIRWA (9116982528)</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="n">
-        <v>81</v>
-      </c>
-      <c r="I54" s="7" t="n">
-        <v>81</v>
-      </c>
-      <c r="J54" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="L54" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="M54" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="7" t="n">
-        <v>101</v>
-      </c>
-      <c r="O54" s="7" t="n">
-        <v>101</v>
-      </c>
-      <c r="P54" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="9" t="inlineStr">
-        <is>
-          <t>पूर्ण मिलान (Exact Match)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>221754</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>पीएम श्री रा.उ.मा.वि. देवलिया कलां (PM SHRI GOVT. SENIOR SECONDARY SCHOOL DEOLIYA KALAN)</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>PEEO DEOLIYA KALAN</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>PURNIMA</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>9414343109</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr">
-        <is>
-          <t>shahrukh khan (7976098421)</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="n">
-        <v>284</v>
-      </c>
-      <c r="I55" s="7" t="n">
-        <v>284</v>
-      </c>
-      <c r="J55" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="7" t="n">
-        <v>242</v>
-      </c>
-      <c r="L55" s="7" t="n">
-        <v>242</v>
-      </c>
-      <c r="M55" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="7" t="n">
-        <v>526</v>
-      </c>
-      <c r="O55" s="7" t="n">
-        <v>526</v>
-      </c>
-      <c r="P55" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="9" t="inlineStr">
-        <is>
-          <t>पूर्ण मिलान (Exact Match)</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="24" customHeight="1" s="26">
-      <c r="A56" s="36" t="inlineStr">
-        <is>
-          <t>कुल राजकीय विद्यालय योग (49 Schools Total)</t>
-        </is>
-      </c>
-      <c r="B56" s="52" t="n"/>
-      <c r="C56" s="52" t="n"/>
-      <c r="D56" s="52" t="n"/>
-      <c r="E56" s="52" t="n"/>
-      <c r="F56" s="52" t="n"/>
-      <c r="G56" s="53" t="n"/>
-      <c r="H56" s="12" t="n">
-        <v>4057</v>
-      </c>
-      <c r="I56" s="12" t="n">
-        <v>4072</v>
-      </c>
-      <c r="J56" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="K56" s="12" t="n">
-        <v>2395</v>
-      </c>
-      <c r="L56" s="12" t="n">
-        <v>2401</v>
-      </c>
-      <c r="M56" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="N56" s="12" t="n">
-        <v>6452</v>
-      </c>
-      <c r="O56" s="12" t="n">
-        <v>6473</v>
-      </c>
-      <c r="P56" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q56" s="14" t="inlineStr">
-        <is>
-          <t>कुल अंतर: +21 (6 विद्यालयों में अंतर, 43 में पूर्ण मिलान)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57"/>
-    <row r="58" ht="22" customHeight="1" s="26">
-      <c r="A58" s="25" t="inlineStr">
-        <is>
-          <t>भाग - 2 : गैर-सरकारी / निजी विद्यालय (8 विद्यालय) - केवल समान परीक्षा पोर्टल पर दर्ज मांग व संस्था प्रधान विवरण</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="18" customHeight="1" s="26">
-      <c r="A59" s="28" t="inlineStr">
-        <is>
-          <t>* नोट: ये 8 निजी विद्यालय समान परीक्षा 2026-27 में शामिल हैं, किंतु 'school enrolment.xlsx' (राजकीय शाला दर्पण नामांकन) में नहीं हैं।</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="24" customHeight="1" s="26">
-      <c r="A60" s="15" t="inlineStr">
-        <is>
-          <t>क्र.सं.</t>
-        </is>
-      </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>विद्यालय कोड</t>
-        </is>
-      </c>
-      <c r="C60" s="15" t="inlineStr">
-        <is>
-          <t>निजी विद्यालय का नाम (School Name)</t>
-        </is>
-      </c>
-      <c r="D60" s="15" t="inlineStr">
-        <is>
-          <t>संबद्ध PEEO</t>
-        </is>
-      </c>
-      <c r="E60" s="15" t="inlineStr">
-        <is>
-          <t>संस्था प्रधान (Principal)</t>
-        </is>
-      </c>
-      <c r="F60" s="15" t="inlineStr">
-        <is>
-          <t>संस्था प्रधान मोबाइल</t>
-        </is>
-      </c>
-      <c r="G60" s="15" t="inlineStr">
-        <is>
-          <t>परीक्षा प्रभारी संपर्क</t>
-        </is>
-      </c>
-      <c r="H60" s="15" t="inlineStr">
-        <is>
-          <t>नामांकन (9-10)</t>
-        </is>
-      </c>
-      <c r="I60" s="15" t="inlineStr">
-        <is>
-          <t>समान परीक्षा (9+10)</t>
-        </is>
-      </c>
-      <c r="J60" s="15" t="inlineStr">
-        <is>
-          <t>अंतर</t>
-        </is>
-      </c>
-      <c r="K60" s="15" t="inlineStr">
-        <is>
-          <t>नामांकन (11-12)</t>
-        </is>
-      </c>
-      <c r="L60" s="15" t="inlineStr">
-        <is>
-          <t>समान परीक्षा (11+12)</t>
-        </is>
-      </c>
-      <c r="M60" s="15" t="inlineStr">
-        <is>
-          <t>अंतर</t>
-        </is>
-      </c>
-      <c r="N60" s="15" t="inlineStr">
-        <is>
-          <t>कुल नामांकन</t>
-        </is>
-      </c>
-      <c r="O60" s="15" t="inlineStr">
-        <is>
-          <t>समान परीक्षा कुल मांग</t>
-        </is>
-      </c>
-      <c r="P60" s="15" t="inlineStr">
-        <is>
-          <t>अंतर</t>
-        </is>
-      </c>
-      <c r="Q60" s="15" t="inlineStr">
-        <is>
-          <t>स्थिति / टिप्पणी</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B61" s="16" t="inlineStr">
-        <is>
-          <t>P16099</t>
-        </is>
-      </c>
-      <c r="C61" s="17" t="inlineStr">
-        <is>
-          <t>GURUKUL KESARI PUBLIC SECONDARY SCHOOL BANDANWARA</t>
-        </is>
-      </c>
-      <c r="D61" s="17" t="inlineStr">
-        <is>
-          <t>PEEO BANDANWARA</t>
-        </is>
-      </c>
-      <c r="E61" s="17" t="inlineStr">
-        <is>
-          <t>SANWAR SINGH</t>
-        </is>
-      </c>
-      <c r="F61" s="16" t="inlineStr">
-        <is>
-          <t>9829395917</t>
-        </is>
-      </c>
-      <c r="G61" s="17" t="inlineStr">
-        <is>
-          <t>NAVEEN KUMAR (9119395917)</t>
-        </is>
-      </c>
-      <c r="H61" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I61" s="8" t="n">
-        <v>483</v>
-      </c>
-      <c r="J61" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K61" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="8" t="n">
-        <v>458</v>
-      </c>
-      <c r="M61" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N61" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O61" s="8" t="n">
-        <v>941</v>
-      </c>
-      <c r="P61" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q61" s="17" t="inlineStr">
-        <is>
-          <t>निजी विद्यालय (समान परीक्षा मांग दर्ज)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B62" s="16" t="inlineStr">
-        <is>
-          <t>P16865</t>
-        </is>
-      </c>
-      <c r="C62" s="17" t="inlineStr">
-        <is>
-          <t>SUMER SENIOR SECONDARY SCHOOL BHINAI</t>
-        </is>
-      </c>
-      <c r="D62" s="17" t="inlineStr">
-        <is>
-          <t>PEEO BHINAY</t>
-        </is>
-      </c>
-      <c r="E62" s="17" t="inlineStr">
-        <is>
-          <t>Manisha</t>
-        </is>
-      </c>
-      <c r="F62" s="16" t="inlineStr">
-        <is>
-          <t>8078661911</t>
-        </is>
-      </c>
-      <c r="G62" s="17" t="inlineStr">
-        <is>
-          <t>Muntazim Khan (9460609888)</t>
-        </is>
-      </c>
-      <c r="H62" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" s="8" t="n">
-        <v>51</v>
-      </c>
-      <c r="J62" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K62" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="M62" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N62" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O62" s="8" t="n">
-        <v>63</v>
-      </c>
-      <c r="P62" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q62" s="17" t="inlineStr">
-        <is>
-          <t>निजी विद्यालय (समान परीक्षा मांग दर्ज)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B63" s="16" t="inlineStr">
-        <is>
-          <t>P16964</t>
-        </is>
-      </c>
-      <c r="C63" s="17" t="inlineStr">
-        <is>
-          <t>SAMRAT INTERNATIONAL SCHOOL BANDANWARA</t>
-        </is>
-      </c>
-      <c r="D63" s="17" t="inlineStr">
-        <is>
-          <t>PEEO BANDANWARA</t>
-        </is>
-      </c>
-      <c r="E63" s="17" t="inlineStr">
-        <is>
-          <t>Kamlesh Kumar sharma</t>
-        </is>
-      </c>
-      <c r="F63" s="16" t="inlineStr">
-        <is>
-          <t>9950000855</t>
-        </is>
-      </c>
-      <c r="G63" s="17" t="inlineStr">
-        <is>
-          <t>Jitendra prajapat (9983606823)</t>
-        </is>
-      </c>
-      <c r="H63" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I63" s="8" t="n">
-        <v>112</v>
-      </c>
-      <c r="J63" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K63" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N63" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O63" s="8" t="n">
-        <v>112</v>
-      </c>
-      <c r="P63" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q63" s="17" t="inlineStr">
-        <is>
-          <t>निजी विद्यालय (समान परीक्षा मांग दर्ज)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B64" s="16" t="inlineStr">
-        <is>
-          <t>P16968</t>
-        </is>
-      </c>
-      <c r="C64" s="17" t="inlineStr">
-        <is>
-          <t>DRONA CHARYA SECONDARY SCHOOL BHINAI</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="inlineStr">
-        <is>
-          <t>PEEO BHINAY</t>
-        </is>
-      </c>
-      <c r="E64" s="17" t="inlineStr">
-        <is>
-          <t>Dronacharya secondary school bhinai</t>
-        </is>
-      </c>
-      <c r="F64" s="16" t="inlineStr">
-        <is>
-          <t>9252971704</t>
-        </is>
-      </c>
-      <c r="G64" s="17" t="inlineStr">
-        <is>
-          <t>Abdul mukaddas (9602560794)</t>
-        </is>
-      </c>
-      <c r="H64" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="J64" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N64" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O64" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="P64" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q64" s="17" t="inlineStr">
-        <is>
-          <t>निजी विद्यालय (समान परीक्षा मांग दर्ज)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B65" s="16" t="inlineStr">
-        <is>
-          <t>P19054</t>
-        </is>
-      </c>
-      <c r="C65" s="17" t="inlineStr">
-        <is>
-          <t>SIDDHARTH INTERNATIONAL SCHOOL BANDANWARA</t>
-        </is>
-      </c>
-      <c r="D65" s="17" t="inlineStr">
-        <is>
-          <t>PEEO BANDANWARA</t>
-        </is>
-      </c>
-      <c r="E65" s="17" t="inlineStr">
-        <is>
-          <t>KAILASH RAWAT</t>
-        </is>
-      </c>
-      <c r="F65" s="16" t="inlineStr">
-        <is>
-          <t>9784505003</t>
-        </is>
-      </c>
-      <c r="G65" s="17" t="inlineStr">
-        <is>
-          <t>NARENDRA SEN (8107179458)</t>
-        </is>
-      </c>
-      <c r="H65" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I65" s="8" t="n">
-        <v>159</v>
-      </c>
-      <c r="J65" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K65" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N65" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O65" s="8" t="n">
-        <v>159</v>
-      </c>
-      <c r="P65" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q65" s="17" t="inlineStr">
-        <is>
-          <t>निजी विद्यालय (समान परीक्षा मांग दर्ज)</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="B66" s="16" t="inlineStr">
-        <is>
-          <t>P19678</t>
-        </is>
-      </c>
-      <c r="C66" s="17" t="inlineStr">
-        <is>
-          <t>SUN RISE CONVENT SCHOOL BHINAI</t>
-        </is>
-      </c>
-      <c r="D66" s="17" t="inlineStr">
-        <is>
-          <t>PEEO BHINAY</t>
-        </is>
-      </c>
-      <c r="E66" s="17" t="inlineStr">
-        <is>
-          <t>SHIVPAL SINGH RATHORE</t>
-        </is>
-      </c>
-      <c r="F66" s="16" t="inlineStr">
-        <is>
-          <t>9413202086</t>
-        </is>
-      </c>
-      <c r="G66" s="17" t="inlineStr">
-        <is>
-          <t>MOHD SHAKEEL DESHWALI (9636239392)</t>
-        </is>
-      </c>
-      <c r="H66" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="J66" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K66" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N66" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O66" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="P66" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q66" s="17" t="inlineStr">
-        <is>
-          <t>निजी विद्यालय (समान परीक्षा मांग दर्ज)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B67" s="16" t="inlineStr">
-        <is>
-          <t>P48759</t>
-        </is>
-      </c>
-      <c r="C67" s="17" t="inlineStr">
-        <is>
-          <t>KUCHAMAN SHIKSHAN SANSTHAN BANDANWARA</t>
-        </is>
-      </c>
-      <c r="D67" s="17" t="inlineStr">
-        <is>
-          <t>PEEO BANDANWARA</t>
-        </is>
-      </c>
-      <c r="E67" s="17" t="inlineStr">
-        <is>
-          <t>RAJENDRA PRASAD VAISHNAV</t>
-        </is>
-      </c>
-      <c r="F67" s="16" t="inlineStr">
-        <is>
-          <t>7877235353</t>
-        </is>
-      </c>
-      <c r="G67" s="17" t="inlineStr">
-        <is>
-          <t>DEVILAL JAT (8949427280)</t>
-        </is>
-      </c>
-      <c r="H67" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I67" s="8" t="n">
-        <v>315</v>
-      </c>
-      <c r="J67" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K67" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="8" t="n">
-        <v>183</v>
-      </c>
-      <c r="M67" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N67" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O67" s="8" t="n">
-        <v>498</v>
-      </c>
-      <c r="P67" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q67" s="17" t="inlineStr">
-        <is>
-          <t>निजी विद्यालय (समान परीक्षा मांग दर्ज)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B68" s="16" t="inlineStr">
-        <is>
-          <t>P55700</t>
-        </is>
-      </c>
-      <c r="C68" s="17" t="inlineStr">
-        <is>
-          <t>TAGORE GLOBAL SCHOOL (EKALSINGHA)</t>
-        </is>
-      </c>
-      <c r="D68" s="17" t="inlineStr">
-        <is>
-          <t>PEEO EKALSEENGA</t>
-        </is>
-      </c>
-      <c r="E68" s="17" t="inlineStr">
-        <is>
-          <t>AALOK MISHRA</t>
-        </is>
-      </c>
-      <c r="F68" s="16" t="inlineStr">
-        <is>
-          <t>9251300400</t>
-        </is>
-      </c>
-      <c r="G68" s="17" t="inlineStr">
-        <is>
-          <t>RAVI SHANKAR SHARMA (8504872321)</t>
-        </is>
-      </c>
-      <c r="H68" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I68" s="8" t="n">
-        <v>92</v>
-      </c>
-      <c r="J68" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K68" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N68" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O68" s="8" t="n">
-        <v>92</v>
-      </c>
-      <c r="P68" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q68" s="17" t="inlineStr">
-        <is>
-          <t>निजी विद्यालय (समान परीक्षा मांग दर्ज)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="24" customHeight="1" s="26">
-      <c r="A69" s="33" t="inlineStr">
-        <is>
-          <t>कुल निजी विद्यालय योग (8 Private Schools Total)</t>
-        </is>
-      </c>
-      <c r="B69" s="52" t="n"/>
-      <c r="C69" s="52" t="n"/>
-      <c r="D69" s="52" t="n"/>
-      <c r="E69" s="52" t="n"/>
-      <c r="F69" s="52" t="n"/>
-      <c r="G69" s="53" t="n"/>
-      <c r="H69" s="33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I69" s="19" t="n">
-        <v>1296</v>
-      </c>
-      <c r="J69" s="33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K69" s="33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="19" t="n">
-        <v>653</v>
-      </c>
-      <c r="M69" s="33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N69" s="33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O69" s="19" t="n">
-        <v>1949</v>
-      </c>
-      <c r="P69" s="33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q69" s="20" t="inlineStr">
-        <is>
-          <t>कुल निजी मांग: 1949</t>
-        </is>
-      </c>
-    </row>
-    <row r="70"/>
-    <row r="71" ht="24" customHeight="1" s="26">
-      <c r="A71" s="40" t="inlineStr">
-        <is>
-          <t>महायोग (GRAND TOTAL: ब्लॉक भिनाय - कुल 57 विद्यालय)</t>
-        </is>
-      </c>
-      <c r="B71" s="54" t="n"/>
-      <c r="C71" s="54" t="n"/>
-      <c r="D71" s="54" t="n"/>
-      <c r="E71" s="54" t="n"/>
-      <c r="F71" s="54" t="n"/>
-      <c r="G71" s="55" t="n"/>
-      <c r="H71" s="21" t="n">
-        <v>4057</v>
-      </c>
-      <c r="I71" s="21" t="n">
-        <v>5368</v>
-      </c>
-      <c r="J71" s="21" t="n">
-        <v>15</v>
-      </c>
-      <c r="K71" s="21" t="n">
-        <v>2395</v>
-      </c>
-      <c r="L71" s="21" t="n">
-        <v>3054</v>
-      </c>
-      <c r="M71" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="N71" s="21" t="n">
-        <v>6452</v>
-      </c>
-      <c r="O71" s="21" t="n">
-        <v>8422</v>
-      </c>
-      <c r="P71" s="21" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q71" s="22" t="inlineStr">
+      <c r="Q71" s="90" t="inlineStr">
         <is>
           <t>राजकीय नामांकन बनाम समान परीक्षा कुल 57 विद्यालयों की मांग</t>
         </is>
